--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,29 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +84,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,11 +98,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -92,6 +133,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1813,4 +1866,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول جیتر (Jitter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Jitter_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1217,6 +1217,76 @@
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JI-015</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ مستقل</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>پنل وصل</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>از پنل قطع PWM را بزن؛ دیالوگ تأیید باید تیره باشد</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>دیالوگ همرنگ پنل، بدون alert سفید</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>استایل تیره</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -746,7 +746,10 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>شماتیک و board_pins.h با کد</t>
+          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
+گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
+گام ۳: قطبیت را هم چک کن: هر دو باید لبهٔ پایین‌رونده (falling) و active-low باشند.
+گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -817,7 +820,9 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>آستانهٔ LM393 را عبور بده (اضافه‌جریان واقعی)</t>
+          <t>گام ۱: شارژ کانال ۱ را فعال کن.
+گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
+گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -888,7 +893,9 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>رویداد حین پردازش تسک کنترل تزریق شود</t>
+          <t>گام ۱: شارژ فعال باشد.
+گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
+گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -959,7 +966,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>دو تریپ پشت‌سرهم؛ رفتار احیا</t>
+          <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
+گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
+گام ۳: 30 ثانیه احیا را نگاه کن: کانال‌ها باید یکی‌یکی و به همان ترتیب تریپ احیا شوند؛ کانال دوم تا نوبتش در صف می‌ماند.
+گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1030,7 +1040,10 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ClearChannel بعد از ریتری</t>
+          <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
+گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
+گام ۳: یک تریپ تازه روی همان کانال بده.
+گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1101,7 +1114,9 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>رویداد مانده از قبل از Init</t>
+          <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
+گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
+گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1172,7 +1187,10 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>تریپ JIT در مود دستی</t>
+          <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
+گام ۲: در مود دستی JIT را تریپ کن.
+گام ۳: 15 ثانیه نگاه کن: کانال پارک می‌شود (وضعیت 5) و ریتری خودکار نباید بیاید؛ شمارش تریپ باید جمع شود.
+گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1243,7 +1261,9 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>از پنل قطع PWM را بزن؛ دیالوگ تأیید باید تیره باشد</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: از پنل دکمهٔ قطع PWM را بزن تا دیالوگ تأیید بیاید.
+گام ۳: دیالوگ باید تیره و هم‌رنگ خود پنل باشد، نه پنجرهٔ سفید alert ویندوز. (3 ثانیه کافی است)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1276,14 +1296,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +71,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +153,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,11 +196,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +286,82 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -517,21 +736,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Jitter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Jitter | مصرف رویدادهای EXTI مقایسه‌گر LM393 (PB2/PB6) و صف احیای تک‌تک JIT شارژر</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -541,21 +760,21 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ورودی‌های open-collector LM393 با عبور جریان از آستانه low می‌شوند؛ firmware روی falling edge تنظیم و low بودن پایه را دوباره چک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>func__BspExti_TakeEvent اتمیک است (PRIMASK)؛ رویداد گم نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>احیای کانال‌های تریپ‌شده تک‌تک و به ترتیب انجام می‌شود.</t>
         </is>
@@ -565,7 +784,7 @@
       <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>هشدار: تریپ عمدی JIT با جریان واقعی فقط با منبع محدودشده و زیر نظارت.</t>
         </is>
@@ -590,161 +809,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Jitter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>JT-001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>نگاشت EXTI</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="40" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
@@ -752,219 +972,219 @@
 گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>PB2=JITTER1، PB6=JITTER2</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>نگاشت درست؛ falling edge؛ active-low</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>ثابت</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>PASS: تطابق</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr"/>
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>JT-002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>رویداد → تریپ شارژر</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال کانال ۱</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ کانال ۱ را فعال کن.
 گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
 گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>JIT1 falling</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>HandleJitTrip کانال ۱: PWM صفر + ورود به صف احیا</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>state=5 کانال ۱</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>JT-003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>اتمیک TakeEvent</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
 گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>رویداد هم‌زمان</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>هیچ رویدادی گم نمی‌شود (بخش بحرانی PRIMASK)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>تریپ در همان پاس ثبت</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>JT-004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>صف احیا تک‌تک</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>هر دو کانال تریپ‌شده</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
 گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
@@ -972,73 +1192,73 @@
 گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>JIT1+JIT2</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>ترتیب حفظ</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>احیای متوالی نه همزمان</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>JT-005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>arm مجدد comparator</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>بعد از safe sequence ریتری</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
 گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
@@ -1046,146 +1266,146 @@
 گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>comparator همان کانال مجدد مسلح می‌شود</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>تریپ بعدی دوباره کار می‌کند</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>JT-006</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>رویداد کهنه در بوت</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>بوت تازه</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
 گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
 گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>بدون تریپ در بوت</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>JT-007</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>مود تست دستی فعال</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
 گام ۲: در مود دستی JIT را تریپ کن.
@@ -1193,141 +1413,391 @@
 گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>پارک تا re-arm</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>JI-015</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: از پنل دکمهٔ قطع PWM را بزن تا دیالوگ تأیید بیاید.
 گام ۳: دیالوگ باید تیره و هم‌رنگ خود پنل باشد، نه پنجرهٔ سفید alert ویندوز. (3 ثانیه کافی است)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>دیالوگ همرنگ پنل، بدون alert سفید</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>استایل تیره</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="P12" s="24" t="n"/>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="Q13" s="27">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="27">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="27">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="27">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="27">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="27">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="27">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="27">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="27">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="27">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="27">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="27">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="27">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="27">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="27">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="27">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="27">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="27">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="27">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="27">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="27">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="27">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="27">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="27">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="27">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="27">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="27">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="27">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="27">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="27">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="27">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="27">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="27">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="27">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="27">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="27">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="27">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="27">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q12"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1341,143 +1811,148 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Jitter</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="39" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>نگاشت</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>PB2/PB6 falling، active-low</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>رویداد منطقی JITTER1/2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>bsp_exti + board_pins.h</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>LM393 open-collector</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>صف احیا</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>تک‌تک، اولین‌تریپ‌اولین‌احیا</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>بدون پامپ همزمان دو کانال</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>charger.c ServiceRetry</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>در مود دستی غیرفعال</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>اتمیک بودن</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>PRIMASK در TakeEvent</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>بدون گم‌شدن رویداد</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>bsp_exti.c (2026-09-22)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>مود دستی</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>بدون ریتری، شمارش جمع</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>سومین تریپ FINAL</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>charger.c HandleJitTrip شاخهٔ manual</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
@@ -1487,6 +1962,12 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1494,6 +1975,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1516,81 +1998,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Jitter</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="38" t="n"/>
+      <c r="G2" s="38" t="n"/>
+      <c r="H2" s="38" t="n"/>
+      <c r="I2" s="38" t="n"/>
+      <c r="J2" s="38" t="n"/>
+      <c r="K2" s="38" t="n"/>
+      <c r="L2" s="38" t="n"/>
+      <c r="M2" s="39" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="28" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -1608,6 +2102,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1620,203 +2115,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Jitter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Jitter — رویدادهای LM393 و صف احیا</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>اسکوپ + تزریق جریان + پنل ESP</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="31">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="31">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="31">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="31">
         <f>IF(7=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/7)</f>
         <v/>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -1835,6 +2332,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1846,105 +2344,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -1958,7 +2464,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1970,55 +2476,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول جیتر (Jitter)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Jitter_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -2031,6 +2538,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,13 @@
       <name val="Tahoma"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -258,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -362,6 +372,13 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -813,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -946,245 +963,98 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>JT-001</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>نگاشت EXTI</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+          <t>JT-002</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>رویداد → تریپ شارژر</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>برد خاموش</t>
-        </is>
-      </c>
-      <c r="E5" s="40" t="inlineStr">
-        <is>
-          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
-گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
-گام ۳: قطبیت را هم چک کن: هر دو باید لبهٔ پایین‌رونده (falling) و active-low باشند.
-گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>PB2=JITTER1، PB6=JITTER2</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>نگاشت درست؛ falling edge؛ active-low</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>ثابت</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>PASS: تطابق</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr"/>
-      <c r="O5" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="19" t="inlineStr"/>
-      <c r="Q5" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>JT-002</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>رویداد → تریپ شارژر</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>شارژ فعال کانال ۱</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>گام ۱: شارژ کانال ۱ را فعال کن.
 گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
 گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>JIT1 falling</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>HandleJitTrip کانال ۱: PWM صفر + ورود به صف احیا</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>state=5 کانال ۱</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr"/>
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>JT-003</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>اتمیک TakeEvent</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>JT-004</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>صف احیا تک‌تک</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>شارژ فعال</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژ فعال باشد.
-گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
-گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>رویداد هم‌زمان</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>هیچ رویدادی گم نمی‌شود (بخش بحرانی PRIMASK)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>تریپ در همان پاس ثبت</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>JT-004</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>صف احیا تک‌تک</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>هر دو کانال تریپ‌شده</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
 گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
@@ -1192,73 +1062,73 @@
 گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>JIT1+JIT2</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>ترتیب حفظ</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>احیای متوالی نه همزمان</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>JT-005</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>arm مجدد comparator</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>بعد از safe sequence ریتری</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
 گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
@@ -1266,146 +1136,146 @@
 گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>comparator همان کانال مجدد مسلح می‌شود</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>تریپ بعدی دوباره کار می‌کند</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>JT-006</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>رویداد کهنه در بوت</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>بوت تازه</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
 گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
 گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>بدون تریپ در بوت</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>JT-007</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>مود تست دستی فعال</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
 گام ۲: در مود دستی JIT را تریپ کن.
@@ -1413,366 +1283,366 @@
 گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>پارک تا re-arm</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>JI-015</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: از پنل دکمهٔ قطع PWM را بزن تا دیالوگ تأیید بیاید.
 گام ۳: دیالوگ باید تیره و هم‌رنگ خود پنل باشد، نه پنجرهٔ سفید alert ویندوز. (3 ثانیه کافی است)</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>دیالوگ همرنگ پنل، بدون alert سفید</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>استایل تیره</t>
         </is>
       </c>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M12" s="22" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="P10" s="24" t="n"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="Q11" s="27">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="Q12" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="Q13" s="27">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="Q14" s="27">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="Q15" s="27">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="27">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="27">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="27">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="27">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="27">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="27">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="27">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="27">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="27">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="27">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="27">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="27">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="27">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="27">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="27">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="27">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="27">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="27">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="27">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="27">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="27">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="27">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="27">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="27">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="27">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="27">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="27">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="27">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="27">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="27">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="27">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="27">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="27">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="27">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="27">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="Q51" s="27">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="Q52" s="27">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q12"/>
+  <autoFilter ref="A4:Q50"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -1786,15 +1656,422 @@
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>JT-001</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>نگاشت EXTI</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>برد خاموش</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
+گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
+گام ۳: قطبیت را هم چک کن: هر دو باید لبهٔ پایین‌رونده (falling) و active-low باشند.
+گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>PB2=JITTER1، PB6=JITTER2</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>نگاشت درست؛ falling edge؛ active-low</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>ثابت</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>PASS: تطابق</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>JT-003</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>اتمیک TakeEvent</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>شارژ فعال</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ فعال باشد.
+گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
+گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>رویداد هم‌زمان</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>هیچ رویدادی گم نمی‌شود (بخش بحرانی PRIMASK)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>تریپ در همان پاس ثبت</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="19" t="n"/>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="27">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="27">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="27">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="27">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="27">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="27">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="27">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="27">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="27">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="27">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="27">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="27">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="27">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="27">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="27">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="27">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="27">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="27">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="27">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q6"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -1972,7 +2249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -2099,7 +2376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -2329,7 +2606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2461,7 +2738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$50</definedName>
@@ -830,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,44 +964,43 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>JT-002</t>
+          <t>JI-015</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>رویداد → تریپ شارژر</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>پنل دیالوگ مستقل</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>پایین</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>شارژ فعال کانال ۱</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ کانال ۱ را فعال کن.
-گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
-گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
+          <t>گام ۱: دیالوگ مربوط به جیتر را در پنل باز کن.
+گام ۲: یک مقدار را بخوان و ببند؛ ببین بقیهٔ پنل و دستگاه عادی کار می‌کنند.</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>JIT1 falling</t>
+          <t>باز و بسته‌کردن دیالوگ جیتر در پنل</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>10s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>HandleJitTrip کانال ۱: PWM صفر + ورود به صف احیا</t>
+          <t>دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -1010,633 +1010,326 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>state=5 کانال ۱</t>
-        </is>
-      </c>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="22" t="inlineStr"/>
+          <t>استقلال دیالوگ = قبول؛ اثر روی بقیه = رد</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P5" s="24" t="inlineStr"/>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="n"/>
       <c r="Q5" s="25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>JT-004</t>
+          <t>JT-008</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>صف احیا تک‌تک</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>شارژ عادی طولانی بدون تریپ بی‌دلیل</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>هر دو کانال تریپ‌شده</t>
+          <t>باتری واقعی وصل و دستگاه در حال شارژ عادی است</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
-گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
-گام ۳: 30 ثانیه احیا را نگاه کن: کانال‌ها باید یکی‌یکی و به همان ترتیب تریپ احیا شوند؛ کانال دوم تا نوبتش در صف می‌ماند.
-گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
+          <t>گام ۱: یک شارژ کامل واقعی (چند ساعت) را از اول تا آخر زیر نظر بگیر.
+گام ۲: دنبال قطع‌ووصل بی‌دلیل شارژ بگرد.</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>JIT1+JIT2</t>
+          <t>یک شارژ کامل واقعی</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>چند ساعت</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
+          <t>شارژ از اول تا آخر پیوسته و بدون قطع‌ووصل بی‌دلیل انجام می‌شود</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>ترتیب حفظ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>احیای متوالی نه همزمان</t>
-        </is>
-      </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+          <t>شارژ پیوسته = قبول؛ هر تریپ بی‌دلیل = رد</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="24" t="n"/>
+      <c r="P6" s="24" t="n"/>
+      <c r="Q6" s="25">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>JT-005</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>arm مجدد comparator</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>بعد از safe sequence ریتری</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
-گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
-گام ۳: یک تریپ تازه روی همان کانال بده.
-گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>comparator همان کانال مجدد مسلح می‌شود</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>تریپ بعدی دوباره کار می‌کند</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q7" s="27">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>JT-006</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>رویداد کهنه در بوت</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>بوت تازه</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
-گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
-گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
-        </is>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
-        <is>
-          <t>بدون تریپ در بوت</t>
-        </is>
-      </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q8" s="27">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>JT-007</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>JIT در مود دستی</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>مود تست دستی فعال</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
-گام ۲: در مود دستی JIT را تریپ کن.
-گام ۳: 15 ثانیه نگاه کن: کانال پارک می‌شود (وضعیت 5) و ریتری خودکار نباید بیاید؛ شمارش تریپ باید جمع شود.
-گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>JIT در مود دستی</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>15s</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>پارک تا re-arm</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q9" s="27">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>JI-015</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>پنل دیالوگ مستقل</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>پنل وصل</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: از پنل دکمهٔ قطع PWM را بزن تا دیالوگ تأیید بیاید.
-گام ۳: دیالوگ باید تیره و هم‌رنگ خود پنل باشد، نه پنجرهٔ سفید alert ویندوز. (3 ثانیه کافی است)</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>دیالوگ همرنگ پنل، بدون alert سفید</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>استایل تیره</t>
-        </is>
-      </c>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="26" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="24" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="25" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q10" s="27">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="Q11" s="27">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
       <c r="Q12" s="27">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="Q13" s="27">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="Q14" s="27">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="Q15" s="27">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="27">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="27">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="27">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="27">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="27">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="27">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="27">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="27">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="27">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="27">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="27">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="27">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="27">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="27">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="27">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="27">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="27">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="27">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="27">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="27">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="27">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="27">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="27">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="27">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="27">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="27">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="27">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="27">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="27">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="27">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="Q46" s="27">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="Q47" s="27">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="Q48" s="27">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="Q49" s="27">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="Q50" s="27">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
@@ -2819,4 +2512,518 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>برنامهٔ تست آزمایشگاهی — ماژول Jitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>JT-002</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>رویداد → تریپ شارژر</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>شارژ فعال کانال ۱</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ کانال ۱ را فعال کن.
+گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
+گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>JIT1 falling</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>HandleJitTrip کانال ۱: PWM صفر + ورود به صف احیا</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>state=5 کانال ۱</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="n"/>
+      <c r="Q5" s="25">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>JT-004</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>صف احیا تک‌تک</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>هر دو کانال تریپ‌شده</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
+گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
+گام ۳: 30 ثانیه احیا را نگاه کن: کانال‌ها باید یکی‌یکی و به همان ترتیب تریپ احیا شوند؛ کانال دوم تا نوبتش در صف می‌ماند.
+گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>JIT1+JIT2</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>30s</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>ترتیب حفظ</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>احیای متوالی نه همزمان</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="24" t="n"/>
+      <c r="Q6" s="25">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>JT-005</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>arm مجدد comparator</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>بعد از safe sequence ریتری</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
+گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
+گام ۳: یک تریپ تازه روی همان کانال بده.
+گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>comparator همان کانال مجدد مسلح می‌شود</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>تریپ بعدی دوباره کار می‌کند</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P7" s="19" t="n"/>
+      <c r="Q7" s="21">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>JT-006</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>رویداد کهنه در بوت</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>بوت تازه</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
+گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
+گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>بدون تریپ در بوت</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="24" t="n"/>
+      <c r="Q8" s="25">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>JT-007</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>JIT در مود دستی</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>مود تست دستی فعال</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
+گام ۲: در مود دستی JIT را تریپ کن.
+گام ۳: 15 ثانیه نگاه کن: کانال پارک می‌شود (وضعیت 5) و ریتری خودکار نباید بیاید؛ شمارش تریپ باید جمع شود.
+گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>JIT در مود دستی</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>15s</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>پارک تا re-arm</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="19" t="n"/>
+      <c r="Q9" s="21">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1"/>
+    <row r="11" ht="54" customHeight="1"/>
+    <row r="12" ht="40.5" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,51 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -269,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -380,6 +425,75 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,55 +868,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Jitter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>Jitter | مصرف رویدادهای EXTI مقایسه‌گر LM393 (PB2/PB6) و صف احیای تک‌تک JIT شارژر</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>ورودی‌های open-collector LM393 با عبور جریان از آستانه low می‌شوند؛ firmware روی falling edge تنظیم و low بودن پایه را دوباره چک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>func__BspExti_TakeEvent اتمیک است (PRIMASK)؛ رویداد گم نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>احیای کانال‌های تریپ‌شده تک‌تک و به ترتیب انجام می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>هشدار: تریپ عمدی JIT با جریان واقعی فقط با منبع محدودشده و زیر نظارت.</t>
         </is>
@@ -854,482 +968,1154 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Jitter</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+      <c r="M1" s="49" t="n"/>
+      <c r="N1" s="49" t="n"/>
+      <c r="O1" s="49" t="n"/>
+      <c r="P1" s="49" t="n"/>
+      <c r="Q1" s="49" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="n"/>
+      <c r="P2" s="49" t="n"/>
+      <c r="Q2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="49" t="n"/>
+      <c r="M3" s="49" t="n"/>
+      <c r="N3" s="49" t="n"/>
+      <c r="O3" s="49" t="n"/>
+      <c r="P3" s="49" t="n"/>
+      <c r="Q3" s="49" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>JI-015</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ مربوط به جیتر را در پنل باز کن.
 گام ۲: یک مقدار را بخوان و ببند؛ ببین بقیهٔ پنل و دستگاه عادی کار می‌کنند.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>باز و بسته‌کردن دیالوگ جیتر در پنل</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>استقلال دیالوگ = قبول؛ اثر روی بقیه = رد</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="K5" s="51" t="n"/>
+      <c r="L5" s="53" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="51" t="n"/>
+      <c r="N5" s="51" t="n"/>
+      <c r="O5" s="52" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="P5" s="52" t="n"/>
+      <c r="Q5" s="54" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>JT-008</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>شارژ عادی طولانی بدون تریپ بی‌دلیل</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>باتری واقعی وصل و دستگاه در حال شارژ عادی است</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>گام ۱: یک شارژ کامل واقعی (چند ساعت) را از اول تا آخر زیر نظر بگیر.
 گام ۲: دنبال قطع‌ووصل بی‌دلیل شارژ بگرد.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>یک شارژ کامل واقعی</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>چند ساعت</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="51" t="inlineStr">
         <is>
           <t>شارژ از اول تا آخر پیوسته و بدون قطع‌ووصل بی‌دلیل انجام می‌شود</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="51" t="inlineStr">
         <is>
           <t>شارژ پیوسته = قبول؛ هر تریپ بی‌دلیل = رد</t>
         </is>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="K6" s="51" t="n"/>
+      <c r="L6" s="53" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="24" t="n"/>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="25">
+      <c r="M6" s="51" t="n"/>
+      <c r="N6" s="51" t="n"/>
+      <c r="O6" s="52" t="n"/>
+      <c r="P6" s="52" t="n"/>
+      <c r="Q6" s="54">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="Q7" s="27">
+      <c r="A7" s="49" t="n"/>
+      <c r="B7" s="49" t="n"/>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="49" t="n"/>
+      <c r="P7" s="49" t="n"/>
+      <c r="Q7" s="55">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="Q8" s="27">
+      <c r="A8" s="49" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="P8" s="49" t="n"/>
+      <c r="Q8" s="55">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="Q9" s="27">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="49" t="n"/>
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="49" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+      <c r="M9" s="49" t="n"/>
+      <c r="N9" s="49" t="n"/>
+      <c r="O9" s="49" t="n"/>
+      <c r="P9" s="49" t="n"/>
+      <c r="Q9" s="55">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="Q10" s="27">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+      <c r="M10" s="49" t="n"/>
+      <c r="N10" s="49" t="n"/>
+      <c r="O10" s="49" t="n"/>
+      <c r="P10" s="49" t="n"/>
+      <c r="Q10" s="55">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="Q11" s="27">
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+      <c r="M11" s="49" t="n"/>
+      <c r="N11" s="49" t="n"/>
+      <c r="O11" s="49" t="n"/>
+      <c r="P11" s="49" t="n"/>
+      <c r="Q11" s="55">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
-      <c r="Q12" s="27">
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="49" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+      <c r="M12" s="49" t="n"/>
+      <c r="N12" s="49" t="n"/>
+      <c r="O12" s="49" t="n"/>
+      <c r="P12" s="49" t="n"/>
+      <c r="Q12" s="55">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="27">
+      <c r="A13" s="49" t="n"/>
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+      <c r="M13" s="49" t="n"/>
+      <c r="N13" s="49" t="n"/>
+      <c r="O13" s="49" t="n"/>
+      <c r="P13" s="49" t="n"/>
+      <c r="Q13" s="55">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="27">
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+      <c r="M14" s="49" t="n"/>
+      <c r="N14" s="49" t="n"/>
+      <c r="O14" s="49" t="n"/>
+      <c r="P14" s="49" t="n"/>
+      <c r="Q14" s="55">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="27">
+      <c r="A15" s="49" t="n"/>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+      <c r="M15" s="49" t="n"/>
+      <c r="N15" s="49" t="n"/>
+      <c r="O15" s="49" t="n"/>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="55">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="27">
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+      <c r="M16" s="49" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="49" t="n"/>
+      <c r="P16" s="49" t="n"/>
+      <c r="Q16" s="55">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="27">
+      <c r="A17" s="49" t="n"/>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+      <c r="M17" s="49" t="n"/>
+      <c r="N17" s="49" t="n"/>
+      <c r="O17" s="49" t="n"/>
+      <c r="P17" s="49" t="n"/>
+      <c r="Q17" s="55">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="27">
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="49" t="n"/>
+      <c r="N18" s="49" t="n"/>
+      <c r="O18" s="49" t="n"/>
+      <c r="P18" s="49" t="n"/>
+      <c r="Q18" s="55">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="27">
+      <c r="A19" s="49" t="n"/>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+      <c r="M19" s="49" t="n"/>
+      <c r="N19" s="49" t="n"/>
+      <c r="O19" s="49" t="n"/>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="55">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="27">
+      <c r="A20" s="49" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+      <c r="M20" s="49" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="49" t="n"/>
+      <c r="P20" s="49" t="n"/>
+      <c r="Q20" s="55">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="27">
+      <c r="A21" s="49" t="n"/>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="49" t="n"/>
+      <c r="N21" s="49" t="n"/>
+      <c r="O21" s="49" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="55">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="27">
+      <c r="A22" s="49" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+      <c r="M22" s="49" t="n"/>
+      <c r="N22" s="49" t="n"/>
+      <c r="O22" s="49" t="n"/>
+      <c r="P22" s="49" t="n"/>
+      <c r="Q22" s="55">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="27">
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="49" t="n"/>
+      <c r="O23" s="49" t="n"/>
+      <c r="P23" s="49" t="n"/>
+      <c r="Q23" s="55">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="27">
+      <c r="A24" s="49" t="n"/>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49" t="n"/>
+      <c r="K24" s="49" t="n"/>
+      <c r="L24" s="49" t="n"/>
+      <c r="M24" s="49" t="n"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="49" t="n"/>
+      <c r="P24" s="49" t="n"/>
+      <c r="Q24" s="55">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="27">
+      <c r="A25" s="49" t="n"/>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49" t="n"/>
+      <c r="K25" s="49" t="n"/>
+      <c r="L25" s="49" t="n"/>
+      <c r="M25" s="49" t="n"/>
+      <c r="N25" s="49" t="n"/>
+      <c r="O25" s="49" t="n"/>
+      <c r="P25" s="49" t="n"/>
+      <c r="Q25" s="55">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="27">
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
+      <c r="K26" s="49" t="n"/>
+      <c r="L26" s="49" t="n"/>
+      <c r="M26" s="49" t="n"/>
+      <c r="N26" s="49" t="n"/>
+      <c r="O26" s="49" t="n"/>
+      <c r="P26" s="49" t="n"/>
+      <c r="Q26" s="55">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="27">
+      <c r="A27" s="49" t="n"/>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49" t="n"/>
+      <c r="K27" s="49" t="n"/>
+      <c r="L27" s="49" t="n"/>
+      <c r="M27" s="49" t="n"/>
+      <c r="N27" s="49" t="n"/>
+      <c r="O27" s="49" t="n"/>
+      <c r="P27" s="49" t="n"/>
+      <c r="Q27" s="55">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="27">
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49" t="n"/>
+      <c r="K28" s="49" t="n"/>
+      <c r="L28" s="49" t="n"/>
+      <c r="M28" s="49" t="n"/>
+      <c r="N28" s="49" t="n"/>
+      <c r="O28" s="49" t="n"/>
+      <c r="P28" s="49" t="n"/>
+      <c r="Q28" s="55">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="27">
+      <c r="A29" s="49" t="n"/>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49" t="n"/>
+      <c r="K29" s="49" t="n"/>
+      <c r="L29" s="49" t="n"/>
+      <c r="M29" s="49" t="n"/>
+      <c r="N29" s="49" t="n"/>
+      <c r="O29" s="49" t="n"/>
+      <c r="P29" s="49" t="n"/>
+      <c r="Q29" s="55">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="27">
+      <c r="A30" s="49" t="n"/>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49" t="n"/>
+      <c r="K30" s="49" t="n"/>
+      <c r="L30" s="49" t="n"/>
+      <c r="M30" s="49" t="n"/>
+      <c r="N30" s="49" t="n"/>
+      <c r="O30" s="49" t="n"/>
+      <c r="P30" s="49" t="n"/>
+      <c r="Q30" s="55">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="27">
+      <c r="A31" s="49" t="n"/>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
+      <c r="J31" s="49" t="n"/>
+      <c r="K31" s="49" t="n"/>
+      <c r="L31" s="49" t="n"/>
+      <c r="M31" s="49" t="n"/>
+      <c r="N31" s="49" t="n"/>
+      <c r="O31" s="49" t="n"/>
+      <c r="P31" s="49" t="n"/>
+      <c r="Q31" s="55">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="27">
+      <c r="A32" s="49" t="n"/>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="49" t="n"/>
+      <c r="K32" s="49" t="n"/>
+      <c r="L32" s="49" t="n"/>
+      <c r="M32" s="49" t="n"/>
+      <c r="N32" s="49" t="n"/>
+      <c r="O32" s="49" t="n"/>
+      <c r="P32" s="49" t="n"/>
+      <c r="Q32" s="55">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="27">
+      <c r="A33" s="49" t="n"/>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="49" t="n"/>
+      <c r="J33" s="49" t="n"/>
+      <c r="K33" s="49" t="n"/>
+      <c r="L33" s="49" t="n"/>
+      <c r="M33" s="49" t="n"/>
+      <c r="N33" s="49" t="n"/>
+      <c r="O33" s="49" t="n"/>
+      <c r="P33" s="49" t="n"/>
+      <c r="Q33" s="55">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="27">
+      <c r="A34" s="49" t="n"/>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="49" t="n"/>
+      <c r="J34" s="49" t="n"/>
+      <c r="K34" s="49" t="n"/>
+      <c r="L34" s="49" t="n"/>
+      <c r="M34" s="49" t="n"/>
+      <c r="N34" s="49" t="n"/>
+      <c r="O34" s="49" t="n"/>
+      <c r="P34" s="49" t="n"/>
+      <c r="Q34" s="55">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="27">
+      <c r="A35" s="49" t="n"/>
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+      <c r="E35" s="49" t="n"/>
+      <c r="F35" s="49" t="n"/>
+      <c r="G35" s="49" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="49" t="n"/>
+      <c r="J35" s="49" t="n"/>
+      <c r="K35" s="49" t="n"/>
+      <c r="L35" s="49" t="n"/>
+      <c r="M35" s="49" t="n"/>
+      <c r="N35" s="49" t="n"/>
+      <c r="O35" s="49" t="n"/>
+      <c r="P35" s="49" t="n"/>
+      <c r="Q35" s="55">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="27">
+      <c r="A36" s="49" t="n"/>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
+      <c r="J36" s="49" t="n"/>
+      <c r="K36" s="49" t="n"/>
+      <c r="L36" s="49" t="n"/>
+      <c r="M36" s="49" t="n"/>
+      <c r="N36" s="49" t="n"/>
+      <c r="O36" s="49" t="n"/>
+      <c r="P36" s="49" t="n"/>
+      <c r="Q36" s="55">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="27">
+      <c r="A37" s="49" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="49" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
+      <c r="J37" s="49" t="n"/>
+      <c r="K37" s="49" t="n"/>
+      <c r="L37" s="49" t="n"/>
+      <c r="M37" s="49" t="n"/>
+      <c r="N37" s="49" t="n"/>
+      <c r="O37" s="49" t="n"/>
+      <c r="P37" s="49" t="n"/>
+      <c r="Q37" s="55">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="27">
+      <c r="A38" s="49" t="n"/>
+      <c r="B38" s="49" t="n"/>
+      <c r="C38" s="49" t="n"/>
+      <c r="D38" s="49" t="n"/>
+      <c r="E38" s="49" t="n"/>
+      <c r="F38" s="49" t="n"/>
+      <c r="G38" s="49" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="49" t="n"/>
+      <c r="J38" s="49" t="n"/>
+      <c r="K38" s="49" t="n"/>
+      <c r="L38" s="49" t="n"/>
+      <c r="M38" s="49" t="n"/>
+      <c r="N38" s="49" t="n"/>
+      <c r="O38" s="49" t="n"/>
+      <c r="P38" s="49" t="n"/>
+      <c r="Q38" s="55">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="27">
+      <c r="A39" s="49" t="n"/>
+      <c r="B39" s="49" t="n"/>
+      <c r="C39" s="49" t="n"/>
+      <c r="D39" s="49" t="n"/>
+      <c r="E39" s="49" t="n"/>
+      <c r="F39" s="49" t="n"/>
+      <c r="G39" s="49" t="n"/>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="49" t="n"/>
+      <c r="J39" s="49" t="n"/>
+      <c r="K39" s="49" t="n"/>
+      <c r="L39" s="49" t="n"/>
+      <c r="M39" s="49" t="n"/>
+      <c r="N39" s="49" t="n"/>
+      <c r="O39" s="49" t="n"/>
+      <c r="P39" s="49" t="n"/>
+      <c r="Q39" s="55">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="27">
+      <c r="A40" s="49" t="n"/>
+      <c r="B40" s="49" t="n"/>
+      <c r="C40" s="49" t="n"/>
+      <c r="D40" s="49" t="n"/>
+      <c r="E40" s="49" t="n"/>
+      <c r="F40" s="49" t="n"/>
+      <c r="G40" s="49" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
+      <c r="J40" s="49" t="n"/>
+      <c r="K40" s="49" t="n"/>
+      <c r="L40" s="49" t="n"/>
+      <c r="M40" s="49" t="n"/>
+      <c r="N40" s="49" t="n"/>
+      <c r="O40" s="49" t="n"/>
+      <c r="P40" s="49" t="n"/>
+      <c r="Q40" s="55">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="27">
+      <c r="A41" s="49" t="n"/>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="49" t="n"/>
+      <c r="D41" s="49" t="n"/>
+      <c r="E41" s="49" t="n"/>
+      <c r="F41" s="49" t="n"/>
+      <c r="G41" s="49" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
+      <c r="J41" s="49" t="n"/>
+      <c r="K41" s="49" t="n"/>
+      <c r="L41" s="49" t="n"/>
+      <c r="M41" s="49" t="n"/>
+      <c r="N41" s="49" t="n"/>
+      <c r="O41" s="49" t="n"/>
+      <c r="P41" s="49" t="n"/>
+      <c r="Q41" s="55">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="27">
+      <c r="A42" s="49" t="n"/>
+      <c r="B42" s="49" t="n"/>
+      <c r="C42" s="49" t="n"/>
+      <c r="D42" s="49" t="n"/>
+      <c r="E42" s="49" t="n"/>
+      <c r="F42" s="49" t="n"/>
+      <c r="G42" s="49" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
+      <c r="J42" s="49" t="n"/>
+      <c r="K42" s="49" t="n"/>
+      <c r="L42" s="49" t="n"/>
+      <c r="M42" s="49" t="n"/>
+      <c r="N42" s="49" t="n"/>
+      <c r="O42" s="49" t="n"/>
+      <c r="P42" s="49" t="n"/>
+      <c r="Q42" s="55">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="27">
+      <c r="A43" s="49" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="49" t="n"/>
+      <c r="D43" s="49" t="n"/>
+      <c r="E43" s="49" t="n"/>
+      <c r="F43" s="49" t="n"/>
+      <c r="G43" s="49" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
+      <c r="J43" s="49" t="n"/>
+      <c r="K43" s="49" t="n"/>
+      <c r="L43" s="49" t="n"/>
+      <c r="M43" s="49" t="n"/>
+      <c r="N43" s="49" t="n"/>
+      <c r="O43" s="49" t="n"/>
+      <c r="P43" s="49" t="n"/>
+      <c r="Q43" s="55">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="27">
+      <c r="A44" s="49" t="n"/>
+      <c r="B44" s="49" t="n"/>
+      <c r="C44" s="49" t="n"/>
+      <c r="D44" s="49" t="n"/>
+      <c r="E44" s="49" t="n"/>
+      <c r="F44" s="49" t="n"/>
+      <c r="G44" s="49" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
+      <c r="J44" s="49" t="n"/>
+      <c r="K44" s="49" t="n"/>
+      <c r="L44" s="49" t="n"/>
+      <c r="M44" s="49" t="n"/>
+      <c r="N44" s="49" t="n"/>
+      <c r="O44" s="49" t="n"/>
+      <c r="P44" s="49" t="n"/>
+      <c r="Q44" s="55">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="27">
+      <c r="A45" s="49" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="n"/>
+      <c r="O45" s="49" t="n"/>
+      <c r="P45" s="49" t="n"/>
+      <c r="Q45" s="55">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
@@ -1384,129 +2170,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+      <c r="M1" s="49" t="n"/>
+      <c r="N1" s="49" t="n"/>
+      <c r="O1" s="49" t="n"/>
+      <c r="P1" s="49" t="n"/>
+      <c r="Q1" s="49" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="43" t="inlineStr">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="n"/>
+      <c r="P2" s="49" t="n"/>
+      <c r="Q2" s="49" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="49" t="n"/>
+      <c r="M3" s="49" t="n"/>
+      <c r="N3" s="49" t="n"/>
+      <c r="O3" s="49" t="n"/>
+      <c r="P3" s="49" t="n"/>
+      <c r="Q3" s="49" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>JT-001</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>نگاشت EXTI</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="58" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
@@ -1514,240 +2350,560 @@
 گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>PB2=JITTER1، PB6=JITTER2</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="58" t="inlineStr">
         <is>
           <t>نگاشت درست؛ falling edge؛ active-low</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="58" t="inlineStr">
         <is>
           <t>ثابت</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="58" t="inlineStr">
         <is>
           <t>PASS: تطابق</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="58" t="n"/>
+      <c r="L5" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="58" t="n"/>
+      <c r="N5" s="58" t="n"/>
+      <c r="O5" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="61" t="n"/>
+      <c r="Q5" s="63" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>JT-003</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>اتمیک TakeEvent</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="58" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
 گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>رویداد هم‌زمان</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>هیچ رویدادی گم نمی‌شود (بخش بحرانی PRIMASK)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>تریپ در همان پاس ثبت</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="58" t="n"/>
+      <c r="L6" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="M6" s="58" t="n"/>
+      <c r="N6" s="58" t="n"/>
+      <c r="O6" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="19" t="n"/>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="P6" s="61" t="n"/>
+      <c r="Q6" s="63" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="27">
+      <c r="A7" s="49" t="n"/>
+      <c r="B7" s="49" t="n"/>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="49" t="n"/>
+      <c r="P7" s="49" t="n"/>
+      <c r="Q7" s="55">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="27">
+      <c r="A8" s="49" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="P8" s="49" t="n"/>
+      <c r="Q8" s="55">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="27">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="49" t="n"/>
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="49" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+      <c r="M9" s="49" t="n"/>
+      <c r="N9" s="49" t="n"/>
+      <c r="O9" s="49" t="n"/>
+      <c r="P9" s="49" t="n"/>
+      <c r="Q9" s="55">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="27">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+      <c r="M10" s="49" t="n"/>
+      <c r="N10" s="49" t="n"/>
+      <c r="O10" s="49" t="n"/>
+      <c r="P10" s="49" t="n"/>
+      <c r="Q10" s="55">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="27">
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+      <c r="M11" s="49" t="n"/>
+      <c r="N11" s="49" t="n"/>
+      <c r="O11" s="49" t="n"/>
+      <c r="P11" s="49" t="n"/>
+      <c r="Q11" s="55">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="27">
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="49" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+      <c r="M12" s="49" t="n"/>
+      <c r="N12" s="49" t="n"/>
+      <c r="O12" s="49" t="n"/>
+      <c r="P12" s="49" t="n"/>
+      <c r="Q12" s="55">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="27">
+      <c r="A13" s="49" t="n"/>
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+      <c r="M13" s="49" t="n"/>
+      <c r="N13" s="49" t="n"/>
+      <c r="O13" s="49" t="n"/>
+      <c r="P13" s="49" t="n"/>
+      <c r="Q13" s="55">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="27">
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+      <c r="M14" s="49" t="n"/>
+      <c r="N14" s="49" t="n"/>
+      <c r="O14" s="49" t="n"/>
+      <c r="P14" s="49" t="n"/>
+      <c r="Q14" s="55">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="27">
+      <c r="A15" s="49" t="n"/>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+      <c r="M15" s="49" t="n"/>
+      <c r="N15" s="49" t="n"/>
+      <c r="O15" s="49" t="n"/>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="55">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="27">
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+      <c r="M16" s="49" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="49" t="n"/>
+      <c r="P16" s="49" t="n"/>
+      <c r="Q16" s="55">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="27">
+      <c r="A17" s="49" t="n"/>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+      <c r="M17" s="49" t="n"/>
+      <c r="N17" s="49" t="n"/>
+      <c r="O17" s="49" t="n"/>
+      <c r="P17" s="49" t="n"/>
+      <c r="Q17" s="55">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="27">
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="49" t="n"/>
+      <c r="N18" s="49" t="n"/>
+      <c r="O18" s="49" t="n"/>
+      <c r="P18" s="49" t="n"/>
+      <c r="Q18" s="55">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="27">
+      <c r="A19" s="49" t="n"/>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+      <c r="M19" s="49" t="n"/>
+      <c r="N19" s="49" t="n"/>
+      <c r="O19" s="49" t="n"/>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="55">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="27">
+      <c r="A20" s="49" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+      <c r="M20" s="49" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="49" t="n"/>
+      <c r="P20" s="49" t="n"/>
+      <c r="Q20" s="55">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="27">
+      <c r="A21" s="49" t="n"/>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="49" t="n"/>
+      <c r="N21" s="49" t="n"/>
+      <c r="O21" s="49" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="55">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="27">
+      <c r="A22" s="49" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+      <c r="M22" s="49" t="n"/>
+      <c r="N22" s="49" t="n"/>
+      <c r="O22" s="49" t="n"/>
+      <c r="P22" s="49" t="n"/>
+      <c r="Q22" s="55">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="27">
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="49" t="n"/>
+      <c r="O23" s="49" t="n"/>
+      <c r="P23" s="49" t="n"/>
+      <c r="Q23" s="55">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="27">
+      <c r="A24" s="49" t="n"/>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49" t="n"/>
+      <c r="K24" s="49" t="n"/>
+      <c r="L24" s="49" t="n"/>
+      <c r="M24" s="49" t="n"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="49" t="n"/>
+      <c r="P24" s="49" t="n"/>
+      <c r="Q24" s="55">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="27">
+      <c r="A25" s="49" t="n"/>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49" t="n"/>
+      <c r="K25" s="49" t="n"/>
+      <c r="L25" s="49" t="n"/>
+      <c r="M25" s="49" t="n"/>
+      <c r="N25" s="49" t="n"/>
+      <c r="O25" s="49" t="n"/>
+      <c r="P25" s="49" t="n"/>
+      <c r="Q25" s="55">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="27">
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
+      <c r="K26" s="49" t="n"/>
+      <c r="L26" s="49" t="n"/>
+      <c r="M26" s="49" t="n"/>
+      <c r="N26" s="49" t="n"/>
+      <c r="O26" s="49" t="n"/>
+      <c r="P26" s="49" t="n"/>
+      <c r="Q26" s="55">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
@@ -1782,147 +2938,153 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-      <c r="E1" s="39" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="64" t="n"/>
+      <c r="C1" s="64" t="n"/>
+      <c r="D1" s="64" t="n"/>
+      <c r="E1" s="65" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="66" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="66" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="66" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>نگاشت</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>PB2/PB6 falling، active-low</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>رویداد منطقی JITTER1/2</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>bsp_exti + board_pins.h</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>LM393 open-collector</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>صف احیا</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>تک‌تک، اولین‌تریپ‌اولین‌احیا</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>بدون پامپ همزمان دو کانال</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>charger.c ServiceRetry</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="67" t="inlineStr">
         <is>
           <t>در مود دستی غیرفعال</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>اتمیک بودن</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>PRIMASK در TakeEvent</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>بدون گم‌شدن رویداد</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>bsp_exti.c (2026-09-22)</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>مود دستی</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>بدون ریتری، شمارش جمع</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>سومین تریپ FINAL</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>charger.c HandleJitTrip شاخهٔ manual</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
@@ -1968,93 +3130,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Jitter</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+      <c r="M1" s="49" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="38" t="n"/>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="39" t="n"/>
+      <c r="B2" s="64" t="n"/>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="64" t="n"/>
+      <c r="E2" s="64" t="n"/>
+      <c r="F2" s="64" t="n"/>
+      <c r="G2" s="64" t="n"/>
+      <c r="H2" s="64" t="n"/>
+      <c r="I2" s="64" t="n"/>
+      <c r="J2" s="64" t="n"/>
+      <c r="K2" s="64" t="n"/>
+      <c r="L2" s="64" t="n"/>
+      <c r="M2" s="65" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="66" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="66" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="66" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
+      <c r="F3" s="66" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="66" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="28" t="inlineStr">
+      <c r="H3" s="66" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="66" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="66" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="66" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="28" t="inlineStr">
+      <c r="L3" s="66" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="66" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2085,209 +3259,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Jitter</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="49" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>Jitter — رویدادهای LM393 و صف احیا</t>
         </is>
       </c>
+      <c r="C5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0)</t>
         </is>
       </c>
+      <c r="C6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>اسکوپ + تزریق جریان + پنل ESP</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="49" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="49" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="70" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="70" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="70">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="70" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="70">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="70" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="70">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="70" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="70" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="70">
         <f>IF(7=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/7)</f>
         <v/>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="70" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2314,117 +3512,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="49" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="49" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="33" t="inlineStr">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="33" t="inlineStr">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="33" t="inlineStr">
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="49" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
+      <c r="B13" s="49" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
+      <c r="B14" s="49" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
+      <c r="B15" s="49" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
+      <c r="B16" s="49" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2446,60 +3663,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول جیتر (Jitter)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Jitter_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="49" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="49" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="49" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2544,207 +3771,255 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Jitter</t>
         </is>
       </c>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+      <c r="M1" s="49" t="n"/>
+      <c r="N1" s="49" t="n"/>
+      <c r="O1" s="49" t="n"/>
+      <c r="P1" s="49" t="n"/>
+      <c r="Q1" s="49" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="49" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="n"/>
+      <c r="P2" s="49" t="n"/>
+      <c r="Q2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="49" t="n"/>
+      <c r="M3" s="49" t="n"/>
+      <c r="N3" s="49" t="n"/>
+      <c r="O3" s="49" t="n"/>
+      <c r="P3" s="49" t="n"/>
+      <c r="Q3" s="49" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="47" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="47" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="47" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="47" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>JT-002</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>رویداد → تریپ شارژر</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="73" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>شارژ فعال کانال ۱</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>گام ۱: شارژ کانال ۱ را فعال کن.
 گام ۲: ورودی JIT1 را یک لبهٔ پایین‌رونده بده تا آستانهٔ LM393 (اضافه‌جریان واقعی) رد شود.
 گام ۳: 10 ثانیه نگاه کن: PWM کانال ۱ باید صفر شود، وضعیت کانال 1 بشود 5 (state=5) و کانال وارد صف احیا شود.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>JIT1 falling</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>HandleJitTrip کانال ۱: PWM صفر + ورود به صف احیا</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>state=5 کانال ۱</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="51" t="n"/>
+      <c r="L5" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="51" t="n"/>
+      <c r="N5" s="51" t="n"/>
+      <c r="O5" s="52" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="25">
+      <c r="P5" s="52" t="n"/>
+      <c r="Q5" s="54">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>JT-004</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>صف احیا تک‌تک</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="73" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>هر دو کانال تریپ‌شده</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
 گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
@@ -2752,72 +4027,72 @@
 گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>JIT1+JIT2</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="51" t="inlineStr">
         <is>
           <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="51" t="inlineStr">
         <is>
           <t>ترتیب حفظ</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="51" t="inlineStr">
         <is>
           <t>احیای متوالی نه همزمان</t>
         </is>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="51" t="n"/>
+      <c r="L6" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M6" s="51" t="n"/>
+      <c r="N6" s="51" t="n"/>
+      <c r="O6" s="52" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="25">
+      <c r="P6" s="52" t="n"/>
+      <c r="Q6" s="54">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>JT-005</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>arm مجدد comparator</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>بعد از safe sequence ریتری</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="58" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
 گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
@@ -2825,144 +4100,144 @@
 گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>comparator همان کانال مجدد مسلح می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="58" t="inlineStr">
         <is>
           <t>تریپ بعدی دوباره کار می‌کند</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K7" s="58" t="n"/>
+      <c r="L7" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="n"/>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="M7" s="58" t="n"/>
+      <c r="N7" s="58" t="n"/>
+      <c r="O7" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="19" t="n"/>
-      <c r="Q7" s="21">
+      <c r="P7" s="61" t="n"/>
+      <c r="Q7" s="63">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>JT-006</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>رویداد کهنه در بوت</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="52" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>بوت تازه</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="51" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
 گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
 گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="51" t="inlineStr">
         <is>
           <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="51" t="inlineStr">
         <is>
           <t>بدون تریپ در بوت</t>
         </is>
       </c>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="51" t="n"/>
+      <c r="L8" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M8" s="51" t="n"/>
+      <c r="N8" s="51" t="n"/>
+      <c r="O8" s="52" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="25">
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="54">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>JT-007</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>مود تست دستی فعال</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="58" t="inlineStr">
         <is>
           <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
 گام ۲: در مود دستی JIT را تریپ کن.
@@ -2970,46 +4245,46 @@
 گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="61" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="58" t="inlineStr">
         <is>
           <t>پارک تا re-arm</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="58" t="inlineStr">
         <is>
           <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
         </is>
       </c>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K9" s="58" t="n"/>
+      <c r="L9" s="62" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M9" s="58" t="n"/>
+      <c r="N9" s="58" t="n"/>
+      <c r="O9" s="61" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="n"/>
-      <c r="Q9" s="21">
+      <c r="P9" s="61" t="n"/>
+      <c r="Q9" s="63">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,6 +186,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -230,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -310,11 +314,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -495,6 +500,9 @@
     <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -861,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -919,6 +927,14 @@
       <c r="A9" s="46" t="inlineStr">
         <is>
           <t>هشدار: تریپ عمدی JIT با جریان واقعی فقط با منبع محدودشده و زیر نظارت.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="74" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -973,22 +989,6 @@
           <t>برنامهٔ تست عملی — ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="49" t="n"/>
-      <c r="C1" s="49" t="n"/>
-      <c r="D1" s="49" t="n"/>
-      <c r="E1" s="49" t="n"/>
-      <c r="F1" s="49" t="n"/>
-      <c r="G1" s="49" t="n"/>
-      <c r="H1" s="49" t="n"/>
-      <c r="I1" s="49" t="n"/>
-      <c r="J1" s="49" t="n"/>
-      <c r="K1" s="49" t="n"/>
-      <c r="L1" s="49" t="n"/>
-      <c r="M1" s="49" t="n"/>
-      <c r="N1" s="49" t="n"/>
-      <c r="O1" s="49" t="n"/>
-      <c r="P1" s="49" t="n"/>
-      <c r="Q1" s="49" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="46" t="inlineStr">
@@ -996,22 +996,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="49" t="n"/>
-      <c r="G2" s="49" t="n"/>
-      <c r="H2" s="49" t="n"/>
-      <c r="I2" s="49" t="n"/>
-      <c r="J2" s="49" t="n"/>
-      <c r="K2" s="49" t="n"/>
-      <c r="L2" s="49" t="n"/>
-      <c r="M2" s="49" t="n"/>
-      <c r="N2" s="49" t="n"/>
-      <c r="O2" s="49" t="n"/>
-      <c r="P2" s="49" t="n"/>
-      <c r="Q2" s="49" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -1019,22 +1003,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
-      <c r="F3" s="49" t="n"/>
-      <c r="G3" s="49" t="n"/>
-      <c r="H3" s="49" t="n"/>
-      <c r="I3" s="49" t="n"/>
-      <c r="J3" s="49" t="n"/>
-      <c r="K3" s="49" t="n"/>
-      <c r="L3" s="49" t="n"/>
-      <c r="M3" s="49" t="n"/>
-      <c r="N3" s="49" t="n"/>
-      <c r="O3" s="49" t="n"/>
-      <c r="P3" s="49" t="n"/>
-      <c r="Q3" s="49" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1084,7 +1052,7 @@
       </c>
       <c r="J4" s="47" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="47" t="inlineStr">
@@ -1123,1002 +1091,884 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="50" t="inlineStr">
         <is>
+          <t>JT-008</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>شارژ عادی طولانی بدون تریپ بی‌دلیل</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>باتری واقعی وصل و دستگاه در حال شارژ عادی است</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>گام ۱: یک شارژ کامل واقعی (چند ساعت) را از اول تا آخر زیر نظر بگیر.
+گام ۲: دنبال قطع‌ووصل بی‌دلیل شارژ بگرد.</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>یک شارژ کامل واقعی</t>
+        </is>
+      </c>
+      <c r="G5" s="52" t="inlineStr">
+        <is>
+          <t>چند ساعت</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>شارژ از اول تا آخر پیوسته و بدون قطع‌ووصل بی‌دلیل انجام می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>باید ببینید: شارژ از اول تا آخر پیوسته و بدون قطع‌ووصل بی‌دلیل انجام می‌شود. اگر تریپ بی‌دلیل دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="51" t="n"/>
+      <c r="L5" s="53" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="51" t="n"/>
+      <c r="N5" s="51" t="n"/>
+      <c r="O5" s="52" t="n"/>
+      <c r="P5" s="52" t="n"/>
+      <c r="Q5" s="54">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
           <t>JI-015</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ مربوط به جیتر را در پنل باز کن.
 گام ۲: یک مقدار را بخوان و ببند؛ ببین بقیهٔ پنل و دستگاه عادی کار می‌کنند.</t>
         </is>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>باز و بسته‌کردن دیالوگ جیتر در پنل</t>
         </is>
       </c>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H6" s="51" t="inlineStr">
         <is>
           <t>دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد</t>
         </is>
       </c>
-      <c r="I5" s="51" t="inlineStr">
+      <c r="I6" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="51" t="inlineStr">
-        <is>
-          <t>استقلال دیالوگ = قبول؛ اثر روی بقیه = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="51" t="n"/>
-      <c r="L5" s="53" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M5" s="51" t="n"/>
-      <c r="N5" s="51" t="n"/>
-      <c r="O5" s="52" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P5" s="52" t="n"/>
-      <c r="Q5" s="54" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
-        <is>
-          <t>JT-008</t>
-        </is>
-      </c>
-      <c r="B6" s="51" t="inlineStr">
-        <is>
-          <t>شارژ عادی طولانی بدون تریپ بی‌دلیل</t>
-        </is>
-      </c>
-      <c r="C6" s="52" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="inlineStr">
-        <is>
-          <t>باتری واقعی وصل و دستگاه در حال شارژ عادی است</t>
-        </is>
-      </c>
-      <c r="E6" s="51" t="inlineStr">
-        <is>
-          <t>گام ۱: یک شارژ کامل واقعی (چند ساعت) را از اول تا آخر زیر نظر بگیر.
-گام ۲: دنبال قطع‌ووصل بی‌دلیل شارژ بگرد.</t>
-        </is>
-      </c>
-      <c r="F6" s="52" t="inlineStr">
-        <is>
-          <t>یک شارژ کامل واقعی</t>
-        </is>
-      </c>
-      <c r="G6" s="52" t="inlineStr">
-        <is>
-          <t>چند ساعت</t>
-        </is>
-      </c>
-      <c r="H6" s="51" t="inlineStr">
-        <is>
-          <t>شارژ از اول تا آخر پیوسته و بدون قطع‌ووصل بی‌دلیل انجام می‌شود</t>
-        </is>
-      </c>
-      <c r="I6" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="51" t="inlineStr">
         <is>
-          <t>شارژ پیوسته = قبول؛ هر تریپ بی‌دلیل = رد</t>
+          <t>باید ببینید: دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد. اگر اثری روی بقیه دیدید، قبول نیست.</t>
         </is>
       </c>
       <c r="K6" s="51" t="n"/>
       <c r="L6" s="53" t="inlineStr">
         <is>
-          <t>در انتظار</t>
+          <t>نیاز به تکرار</t>
         </is>
       </c>
       <c r="M6" s="51" t="n"/>
       <c r="N6" s="51" t="n"/>
-      <c r="O6" s="52" t="n"/>
+      <c r="O6" s="52" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
       <c r="P6" s="52" t="n"/>
       <c r="Q6" s="54">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="49" t="n"/>
-      <c r="B7" s="49" t="n"/>
-      <c r="C7" s="49" t="n"/>
-      <c r="D7" s="49" t="n"/>
-      <c r="E7" s="49" t="n"/>
-      <c r="F7" s="49" t="n"/>
-      <c r="G7" s="49" t="n"/>
-      <c r="H7" s="49" t="n"/>
-      <c r="I7" s="49" t="n"/>
-      <c r="J7" s="49" t="n"/>
-      <c r="K7" s="49" t="n"/>
-      <c r="L7" s="49" t="n"/>
-      <c r="M7" s="49" t="n"/>
-      <c r="N7" s="49" t="n"/>
-      <c r="O7" s="49" t="n"/>
-      <c r="P7" s="49" t="n"/>
-      <c r="Q7" s="55">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="49" t="n"/>
-      <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="49" t="n"/>
-      <c r="G8" s="49" t="n"/>
-      <c r="H8" s="49" t="n"/>
-      <c r="I8" s="49" t="n"/>
-      <c r="J8" s="49" t="n"/>
-      <c r="K8" s="49" t="n"/>
-      <c r="L8" s="49" t="n"/>
-      <c r="M8" s="49" t="n"/>
-      <c r="N8" s="49" t="n"/>
-      <c r="O8" s="49" t="n"/>
-      <c r="P8" s="49" t="n"/>
-      <c r="Q8" s="55">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="49" t="n"/>
-      <c r="B9" s="49" t="n"/>
-      <c r="C9" s="49" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="E9" s="49" t="n"/>
-      <c r="F9" s="49" t="n"/>
-      <c r="G9" s="49" t="n"/>
-      <c r="H9" s="49" t="n"/>
-      <c r="I9" s="49" t="n"/>
-      <c r="J9" s="49" t="n"/>
-      <c r="K9" s="49" t="n"/>
-      <c r="L9" s="49" t="n"/>
-      <c r="M9" s="49" t="n"/>
-      <c r="N9" s="49" t="n"/>
-      <c r="O9" s="49" t="n"/>
-      <c r="P9" s="49" t="n"/>
-      <c r="Q9" s="55">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="49" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="49" t="n"/>
-      <c r="G10" s="49" t="n"/>
-      <c r="H10" s="49" t="n"/>
-      <c r="I10" s="49" t="n"/>
-      <c r="J10" s="49" t="n"/>
-      <c r="K10" s="49" t="n"/>
-      <c r="L10" s="49" t="n"/>
-      <c r="M10" s="49" t="n"/>
-      <c r="N10" s="49" t="n"/>
-      <c r="O10" s="49" t="n"/>
-      <c r="P10" s="49" t="n"/>
-      <c r="Q10" s="55">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="49" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
-      <c r="G11" s="49" t="n"/>
-      <c r="H11" s="49" t="n"/>
-      <c r="I11" s="49" t="n"/>
-      <c r="J11" s="49" t="n"/>
-      <c r="K11" s="49" t="n"/>
-      <c r="L11" s="49" t="n"/>
-      <c r="M11" s="49" t="n"/>
-      <c r="N11" s="49" t="n"/>
-      <c r="O11" s="49" t="n"/>
-      <c r="P11" s="49" t="n"/>
-      <c r="Q11" s="55">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="49" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="49" t="n"/>
-      <c r="G12" s="49" t="n"/>
-      <c r="H12" s="49" t="n"/>
-      <c r="I12" s="49" t="n"/>
-      <c r="J12" s="49" t="n"/>
-      <c r="K12" s="49" t="n"/>
-      <c r="L12" s="49" t="n"/>
-      <c r="M12" s="49" t="n"/>
-      <c r="N12" s="49" t="n"/>
-      <c r="O12" s="49" t="n"/>
-      <c r="P12" s="49" t="n"/>
-      <c r="Q12" s="55">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
-        <v/>
-      </c>
+    <row r="7">
+      <c r="A7" s="75" t="n"/>
+      <c r="B7" s="75" t="n"/>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="75" t="n"/>
+      <c r="F7" s="75" t="n"/>
+      <c r="G7" s="75" t="n"/>
+      <c r="H7" s="75" t="n"/>
+      <c r="I7" s="75" t="n"/>
+      <c r="J7" s="75" t="n"/>
+      <c r="K7" s="75" t="n"/>
+      <c r="L7" s="75" t="n"/>
+      <c r="M7" s="75" t="n"/>
+      <c r="N7" s="75" t="n"/>
+      <c r="O7" s="75" t="n"/>
+      <c r="P7" s="75" t="n"/>
+      <c r="Q7" s="76" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="75" t="n"/>
+      <c r="B8" s="75" t="n"/>
+      <c r="C8" s="75" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="75" t="n"/>
+      <c r="J8" s="75" t="n"/>
+      <c r="K8" s="75" t="n"/>
+      <c r="L8" s="75" t="n"/>
+      <c r="M8" s="75" t="n"/>
+      <c r="N8" s="75" t="n"/>
+      <c r="O8" s="75" t="n"/>
+      <c r="P8" s="75" t="n"/>
+      <c r="Q8" s="76" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="75" t="n"/>
+      <c r="B9" s="75" t="n"/>
+      <c r="C9" s="75" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="75" t="n"/>
+      <c r="F9" s="75" t="n"/>
+      <c r="G9" s="75" t="n"/>
+      <c r="H9" s="75" t="n"/>
+      <c r="I9" s="75" t="n"/>
+      <c r="J9" s="75" t="n"/>
+      <c r="K9" s="75" t="n"/>
+      <c r="L9" s="75" t="n"/>
+      <c r="M9" s="75" t="n"/>
+      <c r="N9" s="75" t="n"/>
+      <c r="O9" s="75" t="n"/>
+      <c r="P9" s="75" t="n"/>
+      <c r="Q9" s="76" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="75" t="n"/>
+      <c r="B10" s="75" t="n"/>
+      <c r="C10" s="75" t="n"/>
+      <c r="D10" s="75" t="n"/>
+      <c r="E10" s="75" t="n"/>
+      <c r="F10" s="75" t="n"/>
+      <c r="G10" s="75" t="n"/>
+      <c r="H10" s="75" t="n"/>
+      <c r="I10" s="75" t="n"/>
+      <c r="J10" s="75" t="n"/>
+      <c r="K10" s="75" t="n"/>
+      <c r="L10" s="75" t="n"/>
+      <c r="M10" s="75" t="n"/>
+      <c r="N10" s="75" t="n"/>
+      <c r="O10" s="75" t="n"/>
+      <c r="P10" s="75" t="n"/>
+      <c r="Q10" s="76" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="75" t="n"/>
+      <c r="B11" s="75" t="n"/>
+      <c r="C11" s="75" t="n"/>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="75" t="n"/>
+      <c r="F11" s="75" t="n"/>
+      <c r="G11" s="75" t="n"/>
+      <c r="H11" s="75" t="n"/>
+      <c r="I11" s="75" t="n"/>
+      <c r="J11" s="75" t="n"/>
+      <c r="K11" s="75" t="n"/>
+      <c r="L11" s="75" t="n"/>
+      <c r="M11" s="75" t="n"/>
+      <c r="N11" s="75" t="n"/>
+      <c r="O11" s="75" t="n"/>
+      <c r="P11" s="75" t="n"/>
+      <c r="Q11" s="76" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="75" t="n"/>
+      <c r="B12" s="75" t="n"/>
+      <c r="C12" s="75" t="n"/>
+      <c r="D12" s="75" t="n"/>
+      <c r="E12" s="75" t="n"/>
+      <c r="F12" s="75" t="n"/>
+      <c r="G12" s="75" t="n"/>
+      <c r="H12" s="75" t="n"/>
+      <c r="I12" s="75" t="n"/>
+      <c r="J12" s="75" t="n"/>
+      <c r="K12" s="75" t="n"/>
+      <c r="L12" s="75" t="n"/>
+      <c r="M12" s="75" t="n"/>
+      <c r="N12" s="75" t="n"/>
+      <c r="O12" s="75" t="n"/>
+      <c r="P12" s="75" t="n"/>
+      <c r="Q12" s="76" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="49" t="n"/>
-      <c r="G13" s="49" t="n"/>
-      <c r="H13" s="49" t="n"/>
-      <c r="I13" s="49" t="n"/>
-      <c r="J13" s="49" t="n"/>
-      <c r="K13" s="49" t="n"/>
-      <c r="L13" s="49" t="n"/>
-      <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="n"/>
-      <c r="O13" s="49" t="n"/>
-      <c r="P13" s="49" t="n"/>
-      <c r="Q13" s="55">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
+      <c r="A13" s="75" t="n"/>
+      <c r="B13" s="75" t="n"/>
+      <c r="C13" s="75" t="n"/>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="75" t="n"/>
+      <c r="F13" s="75" t="n"/>
+      <c r="G13" s="75" t="n"/>
+      <c r="H13" s="75" t="n"/>
+      <c r="I13" s="75" t="n"/>
+      <c r="J13" s="75" t="n"/>
+      <c r="K13" s="75" t="n"/>
+      <c r="L13" s="75" t="n"/>
+      <c r="M13" s="75" t="n"/>
+      <c r="N13" s="75" t="n"/>
+      <c r="O13" s="75" t="n"/>
+      <c r="P13" s="75" t="n"/>
+      <c r="Q13" s="76" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="49" t="n"/>
-      <c r="G14" s="49" t="n"/>
-      <c r="H14" s="49" t="n"/>
-      <c r="I14" s="49" t="n"/>
-      <c r="J14" s="49" t="n"/>
-      <c r="K14" s="49" t="n"/>
-      <c r="L14" s="49" t="n"/>
-      <c r="M14" s="49" t="n"/>
-      <c r="N14" s="49" t="n"/>
-      <c r="O14" s="49" t="n"/>
-      <c r="P14" s="49" t="n"/>
-      <c r="Q14" s="55">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
+      <c r="A14" s="75" t="n"/>
+      <c r="B14" s="75" t="n"/>
+      <c r="C14" s="75" t="n"/>
+      <c r="D14" s="75" t="n"/>
+      <c r="E14" s="75" t="n"/>
+      <c r="F14" s="75" t="n"/>
+      <c r="G14" s="75" t="n"/>
+      <c r="H14" s="75" t="n"/>
+      <c r="I14" s="75" t="n"/>
+      <c r="J14" s="75" t="n"/>
+      <c r="K14" s="75" t="n"/>
+      <c r="L14" s="75" t="n"/>
+      <c r="M14" s="75" t="n"/>
+      <c r="N14" s="75" t="n"/>
+      <c r="O14" s="75" t="n"/>
+      <c r="P14" s="75" t="n"/>
+      <c r="Q14" s="76" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="49" t="n"/>
-      <c r="G15" s="49" t="n"/>
-      <c r="H15" s="49" t="n"/>
-      <c r="I15" s="49" t="n"/>
-      <c r="J15" s="49" t="n"/>
-      <c r="K15" s="49" t="n"/>
-      <c r="L15" s="49" t="n"/>
-      <c r="M15" s="49" t="n"/>
-      <c r="N15" s="49" t="n"/>
-      <c r="O15" s="49" t="n"/>
-      <c r="P15" s="49" t="n"/>
-      <c r="Q15" s="55">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
+      <c r="A15" s="75" t="n"/>
+      <c r="B15" s="75" t="n"/>
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="75" t="n"/>
+      <c r="F15" s="75" t="n"/>
+      <c r="G15" s="75" t="n"/>
+      <c r="H15" s="75" t="n"/>
+      <c r="I15" s="75" t="n"/>
+      <c r="J15" s="75" t="n"/>
+      <c r="K15" s="75" t="n"/>
+      <c r="L15" s="75" t="n"/>
+      <c r="M15" s="75" t="n"/>
+      <c r="N15" s="75" t="n"/>
+      <c r="O15" s="75" t="n"/>
+      <c r="P15" s="75" t="n"/>
+      <c r="Q15" s="76" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="49" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="49" t="n"/>
-      <c r="G16" s="49" t="n"/>
-      <c r="H16" s="49" t="n"/>
-      <c r="I16" s="49" t="n"/>
-      <c r="J16" s="49" t="n"/>
-      <c r="K16" s="49" t="n"/>
-      <c r="L16" s="49" t="n"/>
-      <c r="M16" s="49" t="n"/>
-      <c r="N16" s="49" t="n"/>
-      <c r="O16" s="49" t="n"/>
-      <c r="P16" s="49" t="n"/>
-      <c r="Q16" s="55">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
+      <c r="A16" s="75" t="n"/>
+      <c r="B16" s="75" t="n"/>
+      <c r="C16" s="75" t="n"/>
+      <c r="D16" s="75" t="n"/>
+      <c r="E16" s="75" t="n"/>
+      <c r="F16" s="75" t="n"/>
+      <c r="G16" s="75" t="n"/>
+      <c r="H16" s="75" t="n"/>
+      <c r="I16" s="75" t="n"/>
+      <c r="J16" s="75" t="n"/>
+      <c r="K16" s="75" t="n"/>
+      <c r="L16" s="75" t="n"/>
+      <c r="M16" s="75" t="n"/>
+      <c r="N16" s="75" t="n"/>
+      <c r="O16" s="75" t="n"/>
+      <c r="P16" s="75" t="n"/>
+      <c r="Q16" s="76" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="49" t="n"/>
-      <c r="G17" s="49" t="n"/>
-      <c r="H17" s="49" t="n"/>
-      <c r="I17" s="49" t="n"/>
-      <c r="J17" s="49" t="n"/>
-      <c r="K17" s="49" t="n"/>
-      <c r="L17" s="49" t="n"/>
-      <c r="M17" s="49" t="n"/>
-      <c r="N17" s="49" t="n"/>
-      <c r="O17" s="49" t="n"/>
-      <c r="P17" s="49" t="n"/>
-      <c r="Q17" s="55">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
+      <c r="A17" s="75" t="n"/>
+      <c r="B17" s="75" t="n"/>
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="75" t="n"/>
+      <c r="E17" s="75" t="n"/>
+      <c r="F17" s="75" t="n"/>
+      <c r="G17" s="75" t="n"/>
+      <c r="H17" s="75" t="n"/>
+      <c r="I17" s="75" t="n"/>
+      <c r="J17" s="75" t="n"/>
+      <c r="K17" s="75" t="n"/>
+      <c r="L17" s="75" t="n"/>
+      <c r="M17" s="75" t="n"/>
+      <c r="N17" s="75" t="n"/>
+      <c r="O17" s="75" t="n"/>
+      <c r="P17" s="75" t="n"/>
+      <c r="Q17" s="76" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="49" t="n"/>
-      <c r="G18" s="49" t="n"/>
-      <c r="H18" s="49" t="n"/>
-      <c r="I18" s="49" t="n"/>
-      <c r="J18" s="49" t="n"/>
-      <c r="K18" s="49" t="n"/>
-      <c r="L18" s="49" t="n"/>
-      <c r="M18" s="49" t="n"/>
-      <c r="N18" s="49" t="n"/>
-      <c r="O18" s="49" t="n"/>
-      <c r="P18" s="49" t="n"/>
-      <c r="Q18" s="55">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="A18" s="75" t="n"/>
+      <c r="B18" s="75" t="n"/>
+      <c r="C18" s="75" t="n"/>
+      <c r="D18" s="75" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="75" t="n"/>
+      <c r="G18" s="75" t="n"/>
+      <c r="H18" s="75" t="n"/>
+      <c r="I18" s="75" t="n"/>
+      <c r="J18" s="75" t="n"/>
+      <c r="K18" s="75" t="n"/>
+      <c r="L18" s="75" t="n"/>
+      <c r="M18" s="75" t="n"/>
+      <c r="N18" s="75" t="n"/>
+      <c r="O18" s="75" t="n"/>
+      <c r="P18" s="75" t="n"/>
+      <c r="Q18" s="76" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="n"/>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="49" t="n"/>
-      <c r="G19" s="49" t="n"/>
-      <c r="H19" s="49" t="n"/>
-      <c r="I19" s="49" t="n"/>
-      <c r="J19" s="49" t="n"/>
-      <c r="K19" s="49" t="n"/>
-      <c r="L19" s="49" t="n"/>
-      <c r="M19" s="49" t="n"/>
-      <c r="N19" s="49" t="n"/>
-      <c r="O19" s="49" t="n"/>
-      <c r="P19" s="49" t="n"/>
-      <c r="Q19" s="55">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="A19" s="75" t="n"/>
+      <c r="B19" s="75" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="75" t="n"/>
+      <c r="F19" s="75" t="n"/>
+      <c r="G19" s="75" t="n"/>
+      <c r="H19" s="75" t="n"/>
+      <c r="I19" s="75" t="n"/>
+      <c r="J19" s="75" t="n"/>
+      <c r="K19" s="75" t="n"/>
+      <c r="L19" s="75" t="n"/>
+      <c r="M19" s="75" t="n"/>
+      <c r="N19" s="75" t="n"/>
+      <c r="O19" s="75" t="n"/>
+      <c r="P19" s="75" t="n"/>
+      <c r="Q19" s="76" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="n"/>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="49" t="n"/>
-      <c r="I20" s="49" t="n"/>
-      <c r="J20" s="49" t="n"/>
-      <c r="K20" s="49" t="n"/>
-      <c r="L20" s="49" t="n"/>
-      <c r="M20" s="49" t="n"/>
-      <c r="N20" s="49" t="n"/>
-      <c r="O20" s="49" t="n"/>
-      <c r="P20" s="49" t="n"/>
-      <c r="Q20" s="55">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A20" s="75" t="n"/>
+      <c r="B20" s="75" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="75" t="n"/>
+      <c r="F20" s="75" t="n"/>
+      <c r="G20" s="75" t="n"/>
+      <c r="H20" s="75" t="n"/>
+      <c r="I20" s="75" t="n"/>
+      <c r="J20" s="75" t="n"/>
+      <c r="K20" s="75" t="n"/>
+      <c r="L20" s="75" t="n"/>
+      <c r="M20" s="75" t="n"/>
+      <c r="N20" s="75" t="n"/>
+      <c r="O20" s="75" t="n"/>
+      <c r="P20" s="75" t="n"/>
+      <c r="Q20" s="76" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="n"/>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="49" t="n"/>
-      <c r="D21" s="49" t="n"/>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="49" t="n"/>
-      <c r="G21" s="49" t="n"/>
-      <c r="H21" s="49" t="n"/>
-      <c r="I21" s="49" t="n"/>
-      <c r="J21" s="49" t="n"/>
-      <c r="K21" s="49" t="n"/>
-      <c r="L21" s="49" t="n"/>
-      <c r="M21" s="49" t="n"/>
-      <c r="N21" s="49" t="n"/>
-      <c r="O21" s="49" t="n"/>
-      <c r="P21" s="49" t="n"/>
-      <c r="Q21" s="55">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A21" s="75" t="n"/>
+      <c r="B21" s="75" t="n"/>
+      <c r="C21" s="75" t="n"/>
+      <c r="D21" s="75" t="n"/>
+      <c r="E21" s="75" t="n"/>
+      <c r="F21" s="75" t="n"/>
+      <c r="G21" s="75" t="n"/>
+      <c r="H21" s="75" t="n"/>
+      <c r="I21" s="75" t="n"/>
+      <c r="J21" s="75" t="n"/>
+      <c r="K21" s="75" t="n"/>
+      <c r="L21" s="75" t="n"/>
+      <c r="M21" s="75" t="n"/>
+      <c r="N21" s="75" t="n"/>
+      <c r="O21" s="75" t="n"/>
+      <c r="P21" s="75" t="n"/>
+      <c r="Q21" s="76" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="n"/>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
-      <c r="G22" s="49" t="n"/>
-      <c r="H22" s="49" t="n"/>
-      <c r="I22" s="49" t="n"/>
-      <c r="J22" s="49" t="n"/>
-      <c r="K22" s="49" t="n"/>
-      <c r="L22" s="49" t="n"/>
-      <c r="M22" s="49" t="n"/>
-      <c r="N22" s="49" t="n"/>
-      <c r="O22" s="49" t="n"/>
-      <c r="P22" s="49" t="n"/>
-      <c r="Q22" s="55">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A22" s="75" t="n"/>
+      <c r="B22" s="75" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="75" t="n"/>
+      <c r="F22" s="75" t="n"/>
+      <c r="G22" s="75" t="n"/>
+      <c r="H22" s="75" t="n"/>
+      <c r="I22" s="75" t="n"/>
+      <c r="J22" s="75" t="n"/>
+      <c r="K22" s="75" t="n"/>
+      <c r="L22" s="75" t="n"/>
+      <c r="M22" s="75" t="n"/>
+      <c r="N22" s="75" t="n"/>
+      <c r="O22" s="75" t="n"/>
+      <c r="P22" s="75" t="n"/>
+      <c r="Q22" s="76" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="n"/>
-      <c r="B23" s="49" t="n"/>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
-      <c r="G23" s="49" t="n"/>
-      <c r="H23" s="49" t="n"/>
-      <c r="I23" s="49" t="n"/>
-      <c r="J23" s="49" t="n"/>
-      <c r="K23" s="49" t="n"/>
-      <c r="L23" s="49" t="n"/>
-      <c r="M23" s="49" t="n"/>
-      <c r="N23" s="49" t="n"/>
-      <c r="O23" s="49" t="n"/>
-      <c r="P23" s="49" t="n"/>
-      <c r="Q23" s="55">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A23" s="75" t="n"/>
+      <c r="B23" s="75" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="75" t="n"/>
+      <c r="G23" s="75" t="n"/>
+      <c r="H23" s="75" t="n"/>
+      <c r="I23" s="75" t="n"/>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="75" t="n"/>
+      <c r="L23" s="75" t="n"/>
+      <c r="M23" s="75" t="n"/>
+      <c r="N23" s="75" t="n"/>
+      <c r="O23" s="75" t="n"/>
+      <c r="P23" s="75" t="n"/>
+      <c r="Q23" s="76" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="n"/>
-      <c r="B24" s="49" t="n"/>
-      <c r="C24" s="49" t="n"/>
-      <c r="D24" s="49" t="n"/>
-      <c r="E24" s="49" t="n"/>
-      <c r="F24" s="49" t="n"/>
-      <c r="G24" s="49" t="n"/>
-      <c r="H24" s="49" t="n"/>
-      <c r="I24" s="49" t="n"/>
-      <c r="J24" s="49" t="n"/>
-      <c r="K24" s="49" t="n"/>
-      <c r="L24" s="49" t="n"/>
-      <c r="M24" s="49" t="n"/>
-      <c r="N24" s="49" t="n"/>
-      <c r="O24" s="49" t="n"/>
-      <c r="P24" s="49" t="n"/>
-      <c r="Q24" s="55">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A24" s="75" t="n"/>
+      <c r="B24" s="75" t="n"/>
+      <c r="C24" s="75" t="n"/>
+      <c r="D24" s="75" t="n"/>
+      <c r="E24" s="75" t="n"/>
+      <c r="F24" s="75" t="n"/>
+      <c r="G24" s="75" t="n"/>
+      <c r="H24" s="75" t="n"/>
+      <c r="I24" s="75" t="n"/>
+      <c r="J24" s="75" t="n"/>
+      <c r="K24" s="75" t="n"/>
+      <c r="L24" s="75" t="n"/>
+      <c r="M24" s="75" t="n"/>
+      <c r="N24" s="75" t="n"/>
+      <c r="O24" s="75" t="n"/>
+      <c r="P24" s="75" t="n"/>
+      <c r="Q24" s="76" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="n"/>
-      <c r="B25" s="49" t="n"/>
-      <c r="C25" s="49" t="n"/>
-      <c r="D25" s="49" t="n"/>
-      <c r="E25" s="49" t="n"/>
-      <c r="F25" s="49" t="n"/>
-      <c r="G25" s="49" t="n"/>
-      <c r="H25" s="49" t="n"/>
-      <c r="I25" s="49" t="n"/>
-      <c r="J25" s="49" t="n"/>
-      <c r="K25" s="49" t="n"/>
-      <c r="L25" s="49" t="n"/>
-      <c r="M25" s="49" t="n"/>
-      <c r="N25" s="49" t="n"/>
-      <c r="O25" s="49" t="n"/>
-      <c r="P25" s="49" t="n"/>
-      <c r="Q25" s="55">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A25" s="75" t="n"/>
+      <c r="B25" s="75" t="n"/>
+      <c r="C25" s="75" t="n"/>
+      <c r="D25" s="75" t="n"/>
+      <c r="E25" s="75" t="n"/>
+      <c r="F25" s="75" t="n"/>
+      <c r="G25" s="75" t="n"/>
+      <c r="H25" s="75" t="n"/>
+      <c r="I25" s="75" t="n"/>
+      <c r="J25" s="75" t="n"/>
+      <c r="K25" s="75" t="n"/>
+      <c r="L25" s="75" t="n"/>
+      <c r="M25" s="75" t="n"/>
+      <c r="N25" s="75" t="n"/>
+      <c r="O25" s="75" t="n"/>
+      <c r="P25" s="75" t="n"/>
+      <c r="Q25" s="76" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="n"/>
-      <c r="B26" s="49" t="n"/>
-      <c r="C26" s="49" t="n"/>
-      <c r="D26" s="49" t="n"/>
-      <c r="E26" s="49" t="n"/>
-      <c r="F26" s="49" t="n"/>
-      <c r="G26" s="49" t="n"/>
-      <c r="H26" s="49" t="n"/>
-      <c r="I26" s="49" t="n"/>
-      <c r="J26" s="49" t="n"/>
-      <c r="K26" s="49" t="n"/>
-      <c r="L26" s="49" t="n"/>
-      <c r="M26" s="49" t="n"/>
-      <c r="N26" s="49" t="n"/>
-      <c r="O26" s="49" t="n"/>
-      <c r="P26" s="49" t="n"/>
-      <c r="Q26" s="55">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A26" s="75" t="n"/>
+      <c r="B26" s="75" t="n"/>
+      <c r="C26" s="75" t="n"/>
+      <c r="D26" s="75" t="n"/>
+      <c r="E26" s="75" t="n"/>
+      <c r="F26" s="75" t="n"/>
+      <c r="G26" s="75" t="n"/>
+      <c r="H26" s="75" t="n"/>
+      <c r="I26" s="75" t="n"/>
+      <c r="J26" s="75" t="n"/>
+      <c r="K26" s="75" t="n"/>
+      <c r="L26" s="75" t="n"/>
+      <c r="M26" s="75" t="n"/>
+      <c r="N26" s="75" t="n"/>
+      <c r="O26" s="75" t="n"/>
+      <c r="P26" s="75" t="n"/>
+      <c r="Q26" s="76" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="n"/>
-      <c r="B27" s="49" t="n"/>
-      <c r="C27" s="49" t="n"/>
-      <c r="D27" s="49" t="n"/>
-      <c r="E27" s="49" t="n"/>
-      <c r="F27" s="49" t="n"/>
-      <c r="G27" s="49" t="n"/>
-      <c r="H27" s="49" t="n"/>
-      <c r="I27" s="49" t="n"/>
-      <c r="J27" s="49" t="n"/>
-      <c r="K27" s="49" t="n"/>
-      <c r="L27" s="49" t="n"/>
-      <c r="M27" s="49" t="n"/>
-      <c r="N27" s="49" t="n"/>
-      <c r="O27" s="49" t="n"/>
-      <c r="P27" s="49" t="n"/>
-      <c r="Q27" s="55">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A27" s="75" t="n"/>
+      <c r="B27" s="75" t="n"/>
+      <c r="C27" s="75" t="n"/>
+      <c r="D27" s="75" t="n"/>
+      <c r="E27" s="75" t="n"/>
+      <c r="F27" s="75" t="n"/>
+      <c r="G27" s="75" t="n"/>
+      <c r="H27" s="75" t="n"/>
+      <c r="I27" s="75" t="n"/>
+      <c r="J27" s="75" t="n"/>
+      <c r="K27" s="75" t="n"/>
+      <c r="L27" s="75" t="n"/>
+      <c r="M27" s="75" t="n"/>
+      <c r="N27" s="75" t="n"/>
+      <c r="O27" s="75" t="n"/>
+      <c r="P27" s="75" t="n"/>
+      <c r="Q27" s="76" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="n"/>
-      <c r="B28" s="49" t="n"/>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="49" t="n"/>
-      <c r="E28" s="49" t="n"/>
-      <c r="F28" s="49" t="n"/>
-      <c r="G28" s="49" t="n"/>
-      <c r="H28" s="49" t="n"/>
-      <c r="I28" s="49" t="n"/>
-      <c r="J28" s="49" t="n"/>
-      <c r="K28" s="49" t="n"/>
-      <c r="L28" s="49" t="n"/>
-      <c r="M28" s="49" t="n"/>
-      <c r="N28" s="49" t="n"/>
-      <c r="O28" s="49" t="n"/>
-      <c r="P28" s="49" t="n"/>
-      <c r="Q28" s="55">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A28" s="75" t="n"/>
+      <c r="B28" s="75" t="n"/>
+      <c r="C28" s="75" t="n"/>
+      <c r="D28" s="75" t="n"/>
+      <c r="E28" s="75" t="n"/>
+      <c r="F28" s="75" t="n"/>
+      <c r="G28" s="75" t="n"/>
+      <c r="H28" s="75" t="n"/>
+      <c r="I28" s="75" t="n"/>
+      <c r="J28" s="75" t="n"/>
+      <c r="K28" s="75" t="n"/>
+      <c r="L28" s="75" t="n"/>
+      <c r="M28" s="75" t="n"/>
+      <c r="N28" s="75" t="n"/>
+      <c r="O28" s="75" t="n"/>
+      <c r="P28" s="75" t="n"/>
+      <c r="Q28" s="76" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="n"/>
-      <c r="B29" s="49" t="n"/>
-      <c r="C29" s="49" t="n"/>
-      <c r="D29" s="49" t="n"/>
-      <c r="E29" s="49" t="n"/>
-      <c r="F29" s="49" t="n"/>
-      <c r="G29" s="49" t="n"/>
-      <c r="H29" s="49" t="n"/>
-      <c r="I29" s="49" t="n"/>
-      <c r="J29" s="49" t="n"/>
-      <c r="K29" s="49" t="n"/>
-      <c r="L29" s="49" t="n"/>
-      <c r="M29" s="49" t="n"/>
-      <c r="N29" s="49" t="n"/>
-      <c r="O29" s="49" t="n"/>
-      <c r="P29" s="49" t="n"/>
-      <c r="Q29" s="55">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A29" s="75" t="n"/>
+      <c r="B29" s="75" t="n"/>
+      <c r="C29" s="75" t="n"/>
+      <c r="D29" s="75" t="n"/>
+      <c r="E29" s="75" t="n"/>
+      <c r="F29" s="75" t="n"/>
+      <c r="G29" s="75" t="n"/>
+      <c r="H29" s="75" t="n"/>
+      <c r="I29" s="75" t="n"/>
+      <c r="J29" s="75" t="n"/>
+      <c r="K29" s="75" t="n"/>
+      <c r="L29" s="75" t="n"/>
+      <c r="M29" s="75" t="n"/>
+      <c r="N29" s="75" t="n"/>
+      <c r="O29" s="75" t="n"/>
+      <c r="P29" s="75" t="n"/>
+      <c r="Q29" s="76" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="n"/>
-      <c r="B30" s="49" t="n"/>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="49" t="n"/>
-      <c r="E30" s="49" t="n"/>
-      <c r="F30" s="49" t="n"/>
-      <c r="G30" s="49" t="n"/>
-      <c r="H30" s="49" t="n"/>
-      <c r="I30" s="49" t="n"/>
-      <c r="J30" s="49" t="n"/>
-      <c r="K30" s="49" t="n"/>
-      <c r="L30" s="49" t="n"/>
-      <c r="M30" s="49" t="n"/>
-      <c r="N30" s="49" t="n"/>
-      <c r="O30" s="49" t="n"/>
-      <c r="P30" s="49" t="n"/>
-      <c r="Q30" s="55">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A30" s="75" t="n"/>
+      <c r="B30" s="75" t="n"/>
+      <c r="C30" s="75" t="n"/>
+      <c r="D30" s="75" t="n"/>
+      <c r="E30" s="75" t="n"/>
+      <c r="F30" s="75" t="n"/>
+      <c r="G30" s="75" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="75" t="n"/>
+      <c r="K30" s="75" t="n"/>
+      <c r="L30" s="75" t="n"/>
+      <c r="M30" s="75" t="n"/>
+      <c r="N30" s="75" t="n"/>
+      <c r="O30" s="75" t="n"/>
+      <c r="P30" s="75" t="n"/>
+      <c r="Q30" s="76" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="n"/>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="49" t="n"/>
-      <c r="F31" s="49" t="n"/>
-      <c r="G31" s="49" t="n"/>
-      <c r="H31" s="49" t="n"/>
-      <c r="I31" s="49" t="n"/>
-      <c r="J31" s="49" t="n"/>
-      <c r="K31" s="49" t="n"/>
-      <c r="L31" s="49" t="n"/>
-      <c r="M31" s="49" t="n"/>
-      <c r="N31" s="49" t="n"/>
-      <c r="O31" s="49" t="n"/>
-      <c r="P31" s="49" t="n"/>
-      <c r="Q31" s="55">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A31" s="75" t="n"/>
+      <c r="B31" s="75" t="n"/>
+      <c r="C31" s="75" t="n"/>
+      <c r="D31" s="75" t="n"/>
+      <c r="E31" s="75" t="n"/>
+      <c r="F31" s="75" t="n"/>
+      <c r="G31" s="75" t="n"/>
+      <c r="H31" s="75" t="n"/>
+      <c r="I31" s="75" t="n"/>
+      <c r="J31" s="75" t="n"/>
+      <c r="K31" s="75" t="n"/>
+      <c r="L31" s="75" t="n"/>
+      <c r="M31" s="75" t="n"/>
+      <c r="N31" s="75" t="n"/>
+      <c r="O31" s="75" t="n"/>
+      <c r="P31" s="75" t="n"/>
+      <c r="Q31" s="76" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="n"/>
-      <c r="B32" s="49" t="n"/>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="49" t="n"/>
-      <c r="F32" s="49" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="49" t="n"/>
-      <c r="J32" s="49" t="n"/>
-      <c r="K32" s="49" t="n"/>
-      <c r="L32" s="49" t="n"/>
-      <c r="M32" s="49" t="n"/>
-      <c r="N32" s="49" t="n"/>
-      <c r="O32" s="49" t="n"/>
-      <c r="P32" s="49" t="n"/>
-      <c r="Q32" s="55">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A32" s="75" t="n"/>
+      <c r="B32" s="75" t="n"/>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="75" t="n"/>
+      <c r="E32" s="75" t="n"/>
+      <c r="F32" s="75" t="n"/>
+      <c r="G32" s="75" t="n"/>
+      <c r="H32" s="75" t="n"/>
+      <c r="I32" s="75" t="n"/>
+      <c r="J32" s="75" t="n"/>
+      <c r="K32" s="75" t="n"/>
+      <c r="L32" s="75" t="n"/>
+      <c r="M32" s="75" t="n"/>
+      <c r="N32" s="75" t="n"/>
+      <c r="O32" s="75" t="n"/>
+      <c r="P32" s="75" t="n"/>
+      <c r="Q32" s="76" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="49" t="n"/>
-      <c r="G33" s="49" t="n"/>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
-      <c r="J33" s="49" t="n"/>
-      <c r="K33" s="49" t="n"/>
-      <c r="L33" s="49" t="n"/>
-      <c r="M33" s="49" t="n"/>
-      <c r="N33" s="49" t="n"/>
-      <c r="O33" s="49" t="n"/>
-      <c r="P33" s="49" t="n"/>
-      <c r="Q33" s="55">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A33" s="75" t="n"/>
+      <c r="B33" s="75" t="n"/>
+      <c r="C33" s="75" t="n"/>
+      <c r="D33" s="75" t="n"/>
+      <c r="E33" s="75" t="n"/>
+      <c r="F33" s="75" t="n"/>
+      <c r="G33" s="75" t="n"/>
+      <c r="H33" s="75" t="n"/>
+      <c r="I33" s="75" t="n"/>
+      <c r="J33" s="75" t="n"/>
+      <c r="K33" s="75" t="n"/>
+      <c r="L33" s="75" t="n"/>
+      <c r="M33" s="75" t="n"/>
+      <c r="N33" s="75" t="n"/>
+      <c r="O33" s="75" t="n"/>
+      <c r="P33" s="75" t="n"/>
+      <c r="Q33" s="76" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="n"/>
-      <c r="B34" s="49" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="49" t="n"/>
-      <c r="F34" s="49" t="n"/>
-      <c r="G34" s="49" t="n"/>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
-      <c r="J34" s="49" t="n"/>
-      <c r="K34" s="49" t="n"/>
-      <c r="L34" s="49" t="n"/>
-      <c r="M34" s="49" t="n"/>
-      <c r="N34" s="49" t="n"/>
-      <c r="O34" s="49" t="n"/>
-      <c r="P34" s="49" t="n"/>
-      <c r="Q34" s="55">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A34" s="75" t="n"/>
+      <c r="B34" s="75" t="n"/>
+      <c r="C34" s="75" t="n"/>
+      <c r="D34" s="75" t="n"/>
+      <c r="E34" s="75" t="n"/>
+      <c r="F34" s="75" t="n"/>
+      <c r="G34" s="75" t="n"/>
+      <c r="H34" s="75" t="n"/>
+      <c r="I34" s="75" t="n"/>
+      <c r="J34" s="75" t="n"/>
+      <c r="K34" s="75" t="n"/>
+      <c r="L34" s="75" t="n"/>
+      <c r="M34" s="75" t="n"/>
+      <c r="N34" s="75" t="n"/>
+      <c r="O34" s="75" t="n"/>
+      <c r="P34" s="75" t="n"/>
+      <c r="Q34" s="76" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="n"/>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
-      <c r="G35" s="49" t="n"/>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
-      <c r="J35" s="49" t="n"/>
-      <c r="K35" s="49" t="n"/>
-      <c r="L35" s="49" t="n"/>
-      <c r="M35" s="49" t="n"/>
-      <c r="N35" s="49" t="n"/>
-      <c r="O35" s="49" t="n"/>
-      <c r="P35" s="49" t="n"/>
-      <c r="Q35" s="55">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A35" s="75" t="n"/>
+      <c r="B35" s="75" t="n"/>
+      <c r="C35" s="75" t="n"/>
+      <c r="D35" s="75" t="n"/>
+      <c r="E35" s="75" t="n"/>
+      <c r="F35" s="75" t="n"/>
+      <c r="G35" s="75" t="n"/>
+      <c r="H35" s="75" t="n"/>
+      <c r="I35" s="75" t="n"/>
+      <c r="J35" s="75" t="n"/>
+      <c r="K35" s="75" t="n"/>
+      <c r="L35" s="75" t="n"/>
+      <c r="M35" s="75" t="n"/>
+      <c r="N35" s="75" t="n"/>
+      <c r="O35" s="75" t="n"/>
+      <c r="P35" s="75" t="n"/>
+      <c r="Q35" s="76" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="49" t="n"/>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-      <c r="P36" s="49" t="n"/>
-      <c r="Q36" s="55">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A36" s="75" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
+      <c r="O36" s="75" t="n"/>
+      <c r="P36" s="75" t="n"/>
+      <c r="Q36" s="76" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="n"/>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="49" t="n"/>
-      <c r="L37" s="49" t="n"/>
-      <c r="M37" s="49" t="n"/>
-      <c r="N37" s="49" t="n"/>
-      <c r="O37" s="49" t="n"/>
-      <c r="P37" s="49" t="n"/>
-      <c r="Q37" s="55">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A37" s="75" t="n"/>
+      <c r="B37" s="75" t="n"/>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="75" t="n"/>
+      <c r="E37" s="75" t="n"/>
+      <c r="F37" s="75" t="n"/>
+      <c r="G37" s="75" t="n"/>
+      <c r="H37" s="75" t="n"/>
+      <c r="I37" s="75" t="n"/>
+      <c r="J37" s="75" t="n"/>
+      <c r="K37" s="75" t="n"/>
+      <c r="L37" s="75" t="n"/>
+      <c r="M37" s="75" t="n"/>
+      <c r="N37" s="75" t="n"/>
+      <c r="O37" s="75" t="n"/>
+      <c r="P37" s="75" t="n"/>
+      <c r="Q37" s="76" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="49" t="n"/>
-      <c r="B38" s="49" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="49" t="n"/>
-      <c r="L38" s="49" t="n"/>
-      <c r="M38" s="49" t="n"/>
-      <c r="N38" s="49" t="n"/>
-      <c r="O38" s="49" t="n"/>
-      <c r="P38" s="49" t="n"/>
-      <c r="Q38" s="55">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A38" s="75" t="n"/>
+      <c r="B38" s="75" t="n"/>
+      <c r="C38" s="75" t="n"/>
+      <c r="D38" s="75" t="n"/>
+      <c r="E38" s="75" t="n"/>
+      <c r="F38" s="75" t="n"/>
+      <c r="G38" s="75" t="n"/>
+      <c r="H38" s="75" t="n"/>
+      <c r="I38" s="75" t="n"/>
+      <c r="J38" s="75" t="n"/>
+      <c r="K38" s="75" t="n"/>
+      <c r="L38" s="75" t="n"/>
+      <c r="M38" s="75" t="n"/>
+      <c r="N38" s="75" t="n"/>
+      <c r="O38" s="75" t="n"/>
+      <c r="P38" s="75" t="n"/>
+      <c r="Q38" s="76" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="n"/>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
-      <c r="J39" s="49" t="n"/>
-      <c r="K39" s="49" t="n"/>
-      <c r="L39" s="49" t="n"/>
-      <c r="M39" s="49" t="n"/>
-      <c r="N39" s="49" t="n"/>
-      <c r="O39" s="49" t="n"/>
-      <c r="P39" s="49" t="n"/>
-      <c r="Q39" s="55">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A39" s="75" t="n"/>
+      <c r="B39" s="75" t="n"/>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="75" t="n"/>
+      <c r="H39" s="75" t="n"/>
+      <c r="I39" s="75" t="n"/>
+      <c r="J39" s="75" t="n"/>
+      <c r="K39" s="75" t="n"/>
+      <c r="L39" s="75" t="n"/>
+      <c r="M39" s="75" t="n"/>
+      <c r="N39" s="75" t="n"/>
+      <c r="O39" s="75" t="n"/>
+      <c r="P39" s="75" t="n"/>
+      <c r="Q39" s="76" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="n"/>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="49" t="n"/>
-      <c r="F40" s="49" t="n"/>
-      <c r="G40" s="49" t="n"/>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
-      <c r="J40" s="49" t="n"/>
-      <c r="K40" s="49" t="n"/>
-      <c r="L40" s="49" t="n"/>
-      <c r="M40" s="49" t="n"/>
-      <c r="N40" s="49" t="n"/>
-      <c r="O40" s="49" t="n"/>
-      <c r="P40" s="49" t="n"/>
-      <c r="Q40" s="55">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A40" s="75" t="n"/>
+      <c r="B40" s="75" t="n"/>
+      <c r="C40" s="75" t="n"/>
+      <c r="D40" s="75" t="n"/>
+      <c r="E40" s="75" t="n"/>
+      <c r="F40" s="75" t="n"/>
+      <c r="G40" s="75" t="n"/>
+      <c r="H40" s="75" t="n"/>
+      <c r="I40" s="75" t="n"/>
+      <c r="J40" s="75" t="n"/>
+      <c r="K40" s="75" t="n"/>
+      <c r="L40" s="75" t="n"/>
+      <c r="M40" s="75" t="n"/>
+      <c r="N40" s="75" t="n"/>
+      <c r="O40" s="75" t="n"/>
+      <c r="P40" s="75" t="n"/>
+      <c r="Q40" s="76" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
-      <c r="E41" s="49" t="n"/>
-      <c r="F41" s="49" t="n"/>
-      <c r="G41" s="49" t="n"/>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
-      <c r="J41" s="49" t="n"/>
-      <c r="K41" s="49" t="n"/>
-      <c r="L41" s="49" t="n"/>
-      <c r="M41" s="49" t="n"/>
-      <c r="N41" s="49" t="n"/>
-      <c r="O41" s="49" t="n"/>
-      <c r="P41" s="49" t="n"/>
-      <c r="Q41" s="55">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A41" s="75" t="n"/>
+      <c r="B41" s="75" t="n"/>
+      <c r="C41" s="75" t="n"/>
+      <c r="D41" s="75" t="n"/>
+      <c r="E41" s="75" t="n"/>
+      <c r="F41" s="75" t="n"/>
+      <c r="G41" s="75" t="n"/>
+      <c r="H41" s="75" t="n"/>
+      <c r="I41" s="75" t="n"/>
+      <c r="J41" s="75" t="n"/>
+      <c r="K41" s="75" t="n"/>
+      <c r="L41" s="75" t="n"/>
+      <c r="M41" s="75" t="n"/>
+      <c r="N41" s="75" t="n"/>
+      <c r="O41" s="75" t="n"/>
+      <c r="P41" s="75" t="n"/>
+      <c r="Q41" s="76" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="n"/>
-      <c r="B42" s="49" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
-      <c r="E42" s="49" t="n"/>
-      <c r="F42" s="49" t="n"/>
-      <c r="G42" s="49" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
-      <c r="J42" s="49" t="n"/>
-      <c r="K42" s="49" t="n"/>
-      <c r="L42" s="49" t="n"/>
-      <c r="M42" s="49" t="n"/>
-      <c r="N42" s="49" t="n"/>
-      <c r="O42" s="49" t="n"/>
-      <c r="P42" s="49" t="n"/>
-      <c r="Q42" s="55">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A42" s="75" t="n"/>
+      <c r="B42" s="75" t="n"/>
+      <c r="C42" s="75" t="n"/>
+      <c r="D42" s="75" t="n"/>
+      <c r="E42" s="75" t="n"/>
+      <c r="F42" s="75" t="n"/>
+      <c r="G42" s="75" t="n"/>
+      <c r="H42" s="75" t="n"/>
+      <c r="I42" s="75" t="n"/>
+      <c r="J42" s="75" t="n"/>
+      <c r="K42" s="75" t="n"/>
+      <c r="L42" s="75" t="n"/>
+      <c r="M42" s="75" t="n"/>
+      <c r="N42" s="75" t="n"/>
+      <c r="O42" s="75" t="n"/>
+      <c r="P42" s="75" t="n"/>
+      <c r="Q42" s="76" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="49" t="n"/>
-      <c r="E43" s="49" t="n"/>
-      <c r="F43" s="49" t="n"/>
-      <c r="G43" s="49" t="n"/>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
-      <c r="J43" s="49" t="n"/>
-      <c r="K43" s="49" t="n"/>
-      <c r="L43" s="49" t="n"/>
-      <c r="M43" s="49" t="n"/>
-      <c r="N43" s="49" t="n"/>
-      <c r="O43" s="49" t="n"/>
-      <c r="P43" s="49" t="n"/>
-      <c r="Q43" s="55">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A43" s="75" t="n"/>
+      <c r="B43" s="75" t="n"/>
+      <c r="C43" s="75" t="n"/>
+      <c r="D43" s="75" t="n"/>
+      <c r="E43" s="75" t="n"/>
+      <c r="F43" s="75" t="n"/>
+      <c r="G43" s="75" t="n"/>
+      <c r="H43" s="75" t="n"/>
+      <c r="I43" s="75" t="n"/>
+      <c r="J43" s="75" t="n"/>
+      <c r="K43" s="75" t="n"/>
+      <c r="L43" s="75" t="n"/>
+      <c r="M43" s="75" t="n"/>
+      <c r="N43" s="75" t="n"/>
+      <c r="O43" s="75" t="n"/>
+      <c r="P43" s="75" t="n"/>
+      <c r="Q43" s="76" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="n"/>
-      <c r="B44" s="49" t="n"/>
-      <c r="C44" s="49" t="n"/>
-      <c r="D44" s="49" t="n"/>
-      <c r="E44" s="49" t="n"/>
-      <c r="F44" s="49" t="n"/>
-      <c r="G44" s="49" t="n"/>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="49" t="n"/>
-      <c r="J44" s="49" t="n"/>
-      <c r="K44" s="49" t="n"/>
-      <c r="L44" s="49" t="n"/>
-      <c r="M44" s="49" t="n"/>
-      <c r="N44" s="49" t="n"/>
-      <c r="O44" s="49" t="n"/>
-      <c r="P44" s="49" t="n"/>
-      <c r="Q44" s="55">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A44" s="75" t="n"/>
+      <c r="B44" s="75" t="n"/>
+      <c r="C44" s="75" t="n"/>
+      <c r="D44" s="75" t="n"/>
+      <c r="E44" s="75" t="n"/>
+      <c r="F44" s="75" t="n"/>
+      <c r="G44" s="75" t="n"/>
+      <c r="H44" s="75" t="n"/>
+      <c r="I44" s="75" t="n"/>
+      <c r="J44" s="75" t="n"/>
+      <c r="K44" s="75" t="n"/>
+      <c r="L44" s="75" t="n"/>
+      <c r="M44" s="75" t="n"/>
+      <c r="N44" s="75" t="n"/>
+      <c r="O44" s="75" t="n"/>
+      <c r="P44" s="75" t="n"/>
+      <c r="Q44" s="76" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
-      <c r="E45" s="49" t="n"/>
-      <c r="F45" s="49" t="n"/>
-      <c r="G45" s="49" t="n"/>
-      <c r="H45" s="49" t="n"/>
-      <c r="I45" s="49" t="n"/>
-      <c r="J45" s="49" t="n"/>
-      <c r="K45" s="49" t="n"/>
-      <c r="L45" s="49" t="n"/>
-      <c r="M45" s="49" t="n"/>
-      <c r="N45" s="49" t="n"/>
-      <c r="O45" s="49" t="n"/>
-      <c r="P45" s="49" t="n"/>
-      <c r="Q45" s="55">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A45" s="75" t="n"/>
+      <c r="B45" s="75" t="n"/>
+      <c r="C45" s="75" t="n"/>
+      <c r="D45" s="75" t="n"/>
+      <c r="E45" s="75" t="n"/>
+      <c r="F45" s="75" t="n"/>
+      <c r="G45" s="75" t="n"/>
+      <c r="H45" s="75" t="n"/>
+      <c r="I45" s="75" t="n"/>
+      <c r="J45" s="75" t="n"/>
+      <c r="K45" s="75" t="n"/>
+      <c r="L45" s="75" t="n"/>
+      <c r="M45" s="75" t="n"/>
+      <c r="N45" s="75" t="n"/>
+      <c r="O45" s="75" t="n"/>
+      <c r="P45" s="75" t="n"/>
+      <c r="Q45" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q50"/>
@@ -2128,10 +1978,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -2943,10 +2793,10 @@
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="64" t="n"/>
-      <c r="C1" s="64" t="n"/>
-      <c r="D1" s="64" t="n"/>
-      <c r="E1" s="65" t="n"/>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="39" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="49" t="n"/>
@@ -3135,18 +2985,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="49" t="n"/>
-      <c r="C1" s="49" t="n"/>
-      <c r="D1" s="49" t="n"/>
-      <c r="E1" s="49" t="n"/>
-      <c r="F1" s="49" t="n"/>
-      <c r="G1" s="49" t="n"/>
-      <c r="H1" s="49" t="n"/>
-      <c r="I1" s="49" t="n"/>
-      <c r="J1" s="49" t="n"/>
-      <c r="K1" s="49" t="n"/>
-      <c r="L1" s="49" t="n"/>
-      <c r="M1" s="49" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
@@ -3154,18 +2992,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="64" t="n"/>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="64" t="n"/>
-      <c r="G2" s="64" t="n"/>
-      <c r="H2" s="64" t="n"/>
-      <c r="I2" s="64" t="n"/>
-      <c r="J2" s="64" t="n"/>
-      <c r="K2" s="64" t="n"/>
-      <c r="L2" s="64" t="n"/>
-      <c r="M2" s="65" t="n"/>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="38" t="n"/>
+      <c r="G2" s="38" t="n"/>
+      <c r="H2" s="38" t="n"/>
+      <c r="I2" s="38" t="n"/>
+      <c r="J2" s="38" t="n"/>
+      <c r="K2" s="38" t="n"/>
+      <c r="L2" s="38" t="n"/>
+      <c r="M2" s="39" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="66" t="inlineStr">
@@ -3264,8 +3102,6 @@
           <t>تأیید نهایی اعتبارسنجی — ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="49" t="n"/>
-      <c r="C1" s="49" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="46" t="inlineStr">
@@ -3273,8 +3109,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -3282,8 +3116,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="46" t="inlineStr">
@@ -3668,8 +3500,6 @@
           <t>ماشین حالت ماژول جیتر (Jitter)</t>
         </is>
       </c>
-      <c r="B1" s="49" t="n"/>
-      <c r="C1" s="49" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="49" t="n"/>
@@ -3776,22 +3606,6 @@
           <t>برنامهٔ تست آزمایشگاهی — ماژول Jitter</t>
         </is>
       </c>
-      <c r="B1" s="49" t="n"/>
-      <c r="C1" s="49" t="n"/>
-      <c r="D1" s="49" t="n"/>
-      <c r="E1" s="49" t="n"/>
-      <c r="F1" s="49" t="n"/>
-      <c r="G1" s="49" t="n"/>
-      <c r="H1" s="49" t="n"/>
-      <c r="I1" s="49" t="n"/>
-      <c r="J1" s="49" t="n"/>
-      <c r="K1" s="49" t="n"/>
-      <c r="L1" s="49" t="n"/>
-      <c r="M1" s="49" t="n"/>
-      <c r="N1" s="49" t="n"/>
-      <c r="O1" s="49" t="n"/>
-      <c r="P1" s="49" t="n"/>
-      <c r="Q1" s="49" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="46" t="inlineStr">
@@ -3799,22 +3613,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="49" t="n"/>
-      <c r="G2" s="49" t="n"/>
-      <c r="H2" s="49" t="n"/>
-      <c r="I2" s="49" t="n"/>
-      <c r="J2" s="49" t="n"/>
-      <c r="K2" s="49" t="n"/>
-      <c r="L2" s="49" t="n"/>
-      <c r="M2" s="49" t="n"/>
-      <c r="N2" s="49" t="n"/>
-      <c r="O2" s="49" t="n"/>
-      <c r="P2" s="49" t="n"/>
-      <c r="Q2" s="49" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -3822,22 +3620,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
-      <c r="F3" s="49" t="n"/>
-      <c r="G3" s="49" t="n"/>
-      <c r="H3" s="49" t="n"/>
-      <c r="I3" s="49" t="n"/>
-      <c r="J3" s="49" t="n"/>
-      <c r="K3" s="49" t="n"/>
-      <c r="L3" s="49" t="n"/>
-      <c r="M3" s="49" t="n"/>
-      <c r="N3" s="49" t="n"/>
-      <c r="O3" s="49" t="n"/>
-      <c r="P3" s="49" t="n"/>
-      <c r="Q3" s="49" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="47" t="inlineStr">

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -930,6 +930,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="74" t="inlineStr">
         <is>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -902,14 +902,16 @@
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
-          <t>ورودی‌های open-collector LM393 با عبور جریان از آستانه low می‌شوند؛ firmware روی falling edge تنظیم و low بودن پایه را دوباره چک می‌کند.</t>
+          <t>مقایسه‌گر LM393 خروجی باز (open-collector) دارد.
+وقتی جریان از حد رد شود، پایه پایین می‌آید (low).
+برنامه روی لبهٔ پایین‌رونده تنظیم شده است و دوباره چک می‌کند که پایه هنوز پایین باشد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="46" t="inlineStr">
         <is>
-          <t>func__BspExti_TakeEvent اتمیک است (PRIMASK)؛ رویداد گم نمی‌شود.</t>
+          <t>گرفتن رویداد اتمیک است (با PRIMASK). پس هیچ رویدادی گم نمی‌شود.</t>
         </is>
       </c>
     </row>
@@ -934,8 +936,12 @@
     <row r="11">
       <c r="A11" s="74" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1054,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -1073,12 +1079,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -2128,7 +2134,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -2153,12 +2159,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -2236,7 +2242,7 @@
       <c r="N5" s="58" t="n"/>
       <c r="O5" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="61" t="n"/>
@@ -2309,7 +2315,7 @@
       <c r="N6" s="58" t="n"/>
       <c r="O6" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="61" t="n"/>
@@ -3054,7 +3060,7 @@
       </c>
       <c r="J3" s="66" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="66" t="inlineStr">
@@ -3173,12 +3179,12 @@
     <row r="8">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="46" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="49" t="n"/>
@@ -3665,7 +3671,7 @@
       </c>
       <c r="I4" s="47" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="47" t="inlineStr">
@@ -3690,12 +3696,12 @@
       </c>
       <c r="N4" s="47" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="47" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="47" t="inlineStr">
@@ -3772,7 +3778,7 @@
       <c r="N5" s="51" t="n"/>
       <c r="O5" s="52" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="52" t="n"/>
@@ -3806,8 +3812,8 @@
         <is>
           <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
 گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
-گام ۳: 30 ثانیه احیا را نگاه کن: کانال‌ها باید یکی‌یکی و به همان ترتیب تریپ احیا شوند؛ کانال دوم تا نوبتش در صف می‌ماند.
-گام ۴: احیای هم‌زمان هر دو با هم قبول نیست.</t>
+گام ۳: 30 ثانیه احیا را نگاه کن. کانال‌ها باید یکی‌یکی و به همان ترتیب تریپ احیا شوند.
+گام ۴: کانال دوم تا نوبتش در صف می‌ماند. احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
       <c r="F6" s="52" t="inlineStr">
@@ -3845,7 +3851,7 @@
       <c r="N6" s="51" t="n"/>
       <c r="O6" s="52" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="52" t="n"/>
@@ -3918,7 +3924,7 @@
       <c r="N7" s="58" t="n"/>
       <c r="O7" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="61" t="n"/>
@@ -3990,7 +3996,7 @@
       <c r="N8" s="51" t="n"/>
       <c r="O8" s="52" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="52" t="n"/>
@@ -4063,7 +4069,7 @@
       <c r="N9" s="58" t="n"/>
       <c r="O9" s="61" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="61" t="n"/>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -14,8 +14,8 @@
     <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$50</definedName>
@@ -191,7 +191,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -231,6 +231,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -503,6 +513,32 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -876,7 +912,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Jitter</t>
         </is>
@@ -890,7 +926,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="47" t="inlineStr">
+      <c r="A3" s="78" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -991,7 +1027,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Jitter</t>
         </is>
@@ -1012,87 +1048,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="78" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="78" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="78" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="78" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="78" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="78" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="78" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="78" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="78" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="78" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="78" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="78" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="78" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="78" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="78" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1171,48 +1207,48 @@
           <t>JI-015</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ مربوط به جیتر را در پنل باز کن.
 گام ۲: یک مقدار را بخوان و ببند؛ ببین بقیهٔ پنل و دستگاه عادی کار می‌کنند.</t>
         </is>
       </c>
-      <c r="F6" s="52" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>باز و بسته‌کردن دیالوگ جیتر در پنل</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr">
+      <c r="G6" s="80" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="51" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد</t>
         </is>
       </c>
-      <c r="I6" s="51" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>باید ببینید: دیالوگ مستقل و تمیز کار می‌کند و روی شارژ و چراغ‌ها اثری ندارد. اگر اثری روی بقیه دیدید، قبول نیست.</t>
         </is>
@@ -1225,13 +1261,13 @@
       </c>
       <c r="M6" s="51" t="n"/>
       <c r="N6" s="51" t="n"/>
-      <c r="O6" s="52" t="inlineStr">
+      <c r="O6" s="80" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P6" s="52" t="n"/>
-      <c r="Q6" s="54">
+      <c r="Q6" s="81">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -2000,7 +2036,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2027,7 +2063,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -2092,87 +2128,87 @@
       <c r="Q3" s="49" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="78" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="78" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="78" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="78" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="78" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="78" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="78" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="78" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="78" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="78" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="78" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="78" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="78" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="78" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="78" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -2184,22 +2220,22 @@
           <t>JT-001</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>نگاشت EXTI</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="73" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>برد خاموش</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="83" t="inlineStr">
         <is>
           <t>گام ۱: شماتیک برد و فایل board_pins.h را کنار کد بگذار.
 گام ۲: این نگاشت‌ها را یکی‌یکی چک کن: PB2 = JITTER1 و PB6 = JITTER2.
@@ -2207,27 +2243,27 @@
 گام ۴: قبولی فقط با تطابق کامل هر دو پایه است.</t>
         </is>
       </c>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>PB2=JITTER1، PB6=JITTER2</t>
         </is>
       </c>
-      <c r="G5" s="61" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="58" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>نگاشت درست؛ falling edge؛ active-low</t>
         </is>
       </c>
-      <c r="I5" s="58" t="inlineStr">
+      <c r="I5" s="51" t="inlineStr">
         <is>
           <t>ثابت</t>
         </is>
       </c>
-      <c r="J5" s="58" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>PASS: تطابق</t>
         </is>
@@ -2240,13 +2276,13 @@
       </c>
       <c r="M5" s="58" t="n"/>
       <c r="N5" s="58" t="n"/>
-      <c r="O5" s="61" t="inlineStr">
+      <c r="O5" s="52" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="61" t="n"/>
-      <c r="Q5" s="63" t="inlineStr">
+      <c r="Q5" s="54" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2258,49 +2294,49 @@
           <t>JT-003</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>اتمیک TakeEvent</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>شارژ فعال</t>
         </is>
       </c>
-      <c r="E6" s="58" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>گام ۱: شارژ فعال باشد.
 گام ۲: دقیقاً حین پردازش تسک کنترل، یک رویداد JIT تزریق کن (هم‌زمان با پاس تسک).
 گام ۳: ببین تریپ در همان پاس ثبت شده باشد؛ بخش بحرانی با PRIMASK نباید هیچ رویدادی را گم کند.</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>رویداد هم‌زمان</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="58" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>هیچ رویدادی گم نمی‌شود (بخش بحرانی PRIMASK)</t>
         </is>
       </c>
-      <c r="I6" s="58" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="58" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>تریپ در همان پاس ثبت</t>
         </is>
@@ -2313,13 +2349,13 @@
       </c>
       <c r="M6" s="58" t="n"/>
       <c r="N6" s="58" t="n"/>
-      <c r="O6" s="61" t="inlineStr">
+      <c r="O6" s="80" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="61" t="n"/>
-      <c r="Q6" s="63" t="inlineStr">
+      <c r="Q6" s="81" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2795,7 +2831,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Jitter</t>
         </is>
@@ -2987,14 +3023,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Jitter</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
@@ -3104,7 +3140,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Jitter</t>
         </is>
@@ -3339,7 +3375,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3351,7 +3387,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -3407,7 +3443,7 @@
       <c r="B7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -3443,7 +3479,7 @@
       <c r="B12" s="49" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -3490,98 +3526,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>ماشین حالت ماژول جیتر (Jitter)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="49" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>حالت‌ها و گذارهای همین ماژول</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Jitter_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="49" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>../../../Documentation/System_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" s="49" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>راهنمای رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C5" s="49" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>بازتولید</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>python3 tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-      <c r="C6" s="49" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3608,7 +3553,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Jitter</t>
         </is>
@@ -3629,87 +3574,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="78" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="78" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="78" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="78" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="78" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="47" t="inlineStr">
+      <c r="H4" s="78" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="47" t="inlineStr">
+      <c r="I4" s="78" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="78" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="78" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="78" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="47" t="inlineStr">
+      <c r="M4" s="78" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="47" t="inlineStr">
+      <c r="N4" s="78" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O4" s="78" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="47" t="inlineStr">
+      <c r="P4" s="78" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="47" t="inlineStr">
+      <c r="Q4" s="78" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3793,22 +3738,22 @@
           <t>JT-004</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>صف احیا تک‌تک</t>
         </is>
       </c>
-      <c r="C6" s="73" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>هر دو کانال تریپ‌شده</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>گام ۱: هر دو کانال را در حال شارژ داشته باش.
 گام ۲: اول JIT1 و بلافاصله JIT2 را تریپ کن.
@@ -3816,27 +3761,27 @@
 گام ۴: کانال دوم تا نوبتش در صف می‌ماند. احیای هم‌زمان هر دو با هم قبول نیست.</t>
         </is>
       </c>
-      <c r="F6" s="52" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>JIT1+JIT2</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr">
+      <c r="G6" s="80" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="H6" s="51" t="inlineStr">
+      <c r="H6" s="79" t="inlineStr">
         <is>
           <t>احیا یکی‌یکی به ترتیب تریپ؛ کانال دوم در صف می‌ماند</t>
         </is>
       </c>
-      <c r="I6" s="51" t="inlineStr">
+      <c r="I6" s="79" t="inlineStr">
         <is>
           <t>ترتیب حفظ</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="J6" s="79" t="inlineStr">
         <is>
           <t>احیای متوالی نه همزمان</t>
         </is>
@@ -3849,13 +3794,13 @@
       </c>
       <c r="M6" s="51" t="n"/>
       <c r="N6" s="51" t="n"/>
-      <c r="O6" s="52" t="inlineStr">
+      <c r="O6" s="80" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="52" t="n"/>
-      <c r="Q6" s="54">
+      <c r="Q6" s="81">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -3866,22 +3811,22 @@
           <t>JT-005</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>arm مجدد comparator</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="73" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>بعد از safe sequence ریتری</t>
         </is>
       </c>
-      <c r="E7" s="58" t="inlineStr">
+      <c r="E7" s="51" t="inlineStr">
         <is>
           <t>گام ۱: یک کانال را تریپ کن و بگذار توالی امن (safe sequence) تمام شود و ریتری انجام شود.
 گام ۲: بعد از ریتری، پاک‌سازی کانال (ClearChannel) را بررسی کن.
@@ -3889,27 +3834,27 @@
 گام ۴: comparator همان کانال باید دوباره مسلح شده باشد و تریپ تازه مثل بار اول کار کند.</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
+      <c r="F7" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="61" t="inlineStr">
+      <c r="G7" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="58" t="inlineStr">
+      <c r="H7" s="51" t="inlineStr">
         <is>
           <t>comparator همان کانال مجدد مسلح می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="58" t="inlineStr">
+      <c r="I7" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="58" t="inlineStr">
+      <c r="J7" s="51" t="inlineStr">
         <is>
           <t>تریپ بعدی دوباره کار می‌کند</t>
         </is>
@@ -3922,13 +3867,13 @@
       </c>
       <c r="M7" s="58" t="n"/>
       <c r="N7" s="58" t="n"/>
-      <c r="O7" s="61" t="inlineStr">
+      <c r="O7" s="52" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="61" t="n"/>
-      <c r="Q7" s="63">
+      <c r="Q7" s="54">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -3939,49 +3884,49 @@
           <t>JT-006</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>رویداد کهنه در بوت</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="80" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="79" t="inlineStr">
         <is>
           <t>بوت تازه</t>
         </is>
       </c>
-      <c r="E8" s="51" t="inlineStr">
+      <c r="E8" s="79" t="inlineStr">
         <is>
           <t>گام ۱: یک رویداد JIT بساز ولی قبل از اینکه پردازش شود، وضعیت را طوری نگه دار که رویداد «از قبل» مانده باشد.
 گام ۲: برد را تازه بوت کن (Init از نو اجرا شود).
 گام ۳: بعد از بوت نگاه کن: رویداد مانده باید در Init پاک شده باشد و هیچ تریپ تازه‌ای در بوت نباید زده شود.</t>
         </is>
       </c>
-      <c r="F8" s="52" t="inlineStr">
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="52" t="inlineStr">
+      <c r="G8" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="51" t="inlineStr">
+      <c r="H8" s="79" t="inlineStr">
         <is>
           <t>پاک می‌شود؛ تریپ تازه‌ای نمی‌زند</t>
         </is>
       </c>
-      <c r="I8" s="51" t="inlineStr">
+      <c r="I8" s="79" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="51" t="inlineStr">
+      <c r="J8" s="79" t="inlineStr">
         <is>
           <t>بدون تریپ در بوت</t>
         </is>
@@ -3994,13 +3939,13 @@
       </c>
       <c r="M8" s="51" t="n"/>
       <c r="N8" s="51" t="n"/>
-      <c r="O8" s="52" t="inlineStr">
+      <c r="O8" s="80" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="52" t="n"/>
-      <c r="Q8" s="54">
+      <c r="Q8" s="81">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -4011,22 +3956,22 @@
           <t>JT-007</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="73" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>مود تست دستی فعال</t>
         </is>
       </c>
-      <c r="E9" s="58" t="inlineStr">
+      <c r="E9" s="51" t="inlineStr">
         <is>
           <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
 گام ۲: در مود دستی JIT را تریپ کن.
@@ -4034,27 +3979,27 @@
 گام ۴: فقط وقتی از پنل دوباره duty بفرستی کانال مسلح می‌شود؛ تریپ سوم در همین مود باید FINAL_FAULT بدهد.</t>
         </is>
       </c>
-      <c r="F9" s="61" t="inlineStr">
+      <c r="F9" s="52" t="inlineStr">
         <is>
           <t>JIT در مود دستی</t>
         </is>
       </c>
-      <c r="G9" s="61" t="inlineStr">
+      <c r="G9" s="52" t="inlineStr">
         <is>
           <t>15s</t>
         </is>
       </c>
-      <c r="H9" s="58" t="inlineStr">
+      <c r="H9" s="51" t="inlineStr">
         <is>
           <t>پارک بدون ریتری خودکار؛ شمارش تریپ جمع می‌شود؛ سومین تریپ FINAL_FAULT</t>
         </is>
       </c>
-      <c r="I9" s="58" t="inlineStr">
+      <c r="I9" s="51" t="inlineStr">
         <is>
           <t>پارک تا re-arm</t>
         </is>
       </c>
-      <c r="J9" s="58" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>state=5؛ فقط ارسال مجدد duty مسلح می‌کند</t>
         </is>
@@ -4067,13 +4012,13 @@
       </c>
       <c r="M9" s="58" t="n"/>
       <c r="N9" s="58" t="n"/>
-      <c r="O9" s="61" t="inlineStr">
+      <c r="O9" s="52" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="61" t="n"/>
-      <c r="Q9" s="63">
+      <c r="Q9" s="54">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -4090,4 +4035,87 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول جیتر (Jitter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Jitter_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -190,8 +190,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -241,6 +257,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -329,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -539,6 +560,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -905,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -968,7 +1010,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="74" t="inlineStr">
         <is>
@@ -978,6 +1019,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="87" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B13" s="88" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1024,12 +1077,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="77" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Jitter</t>
+        </is>
+      </c>
+      <c r="T1" s="89" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1039,6 +1100,14 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="T2" s="90" t="inlineStr">
+        <is>
+          <t>کانال تریپ‌شده (0=هیچ، 1 یا 2)</t>
+        </is>
+      </c>
+      <c r="U2" s="91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -1046,6 +1115,11 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="T3" s="92" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="78" t="inlineStr">
@@ -1131,6 +1205,11 @@
       <c r="Q4" s="78" t="inlineStr">
         <is>
           <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="R4" s="78" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
         </is>
       </c>
     </row>
@@ -1200,6 +1279,10 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="88">
+        <f>IF($U$2=0,"بدون تریپ: شارژ عادی و پیوسته ادامه دارد","کانال "&amp;$U$2&amp;" تریپ شده: همان کانال می‌ایستد و به نوبت احیا می‌شود")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="50" t="inlineStr">
@@ -1270,6 +1353,11 @@
       <c r="Q6" s="81">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
+      </c>
+      <c r="R6" s="93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2015,9 +2103,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q50"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
@@ -4044,7 +4134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4058,7 +4148,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4107,7 +4196,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Jitter/Jitter_Validation.xlsx
+++ b/Firmware/Modules/Jitter/Jitter_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$50</definedName>
